--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>6954</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.9103285770388795</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>7119</v>
+        <v>165</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.9319282628616311</v>
+        <v>0.02159968582275167</v>
       </c>
     </row>
     <row r="8">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01714884147139678</v>
+        <v>0.007330802461055112</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>308</v>
+        <v>383</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.04031941353580312</v>
+        <v>0.05013745254614478</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15417,9 +15417,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15767,9 +15767,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15802,9 +15802,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16047,9 +16047,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16117,9 +16117,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16257,9 +16257,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16327,9 +16327,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16362,9 +16362,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16397,9 +16397,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16467,9 +16467,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16502,9 +16502,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16537,9 +16537,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16572,9 +16572,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16642,9 +16642,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16747,9 +16747,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16782,9 +16782,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16852,9 +16852,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16922,9 +16922,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16957,9 +16957,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16992,9 +16992,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17027,9 +17027,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17062,9 +17062,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17097,9 +17097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17132,9 +17132,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17167,9 +17167,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17202,9 +17202,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17237,9 +17237,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17272,9 +17272,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17307,9 +17307,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17342,9 +17342,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17377,9 +17377,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17412,9 +17412,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17482,9 +17482,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17517,9 +17517,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17552,9 +17552,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17587,9 +17587,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17622,9 +17622,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17657,9 +17657,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17692,9 +17692,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17727,9 +17727,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18030,9 +18030,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18415,9 +18415,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18555,9 +18555,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18590,9 +18590,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18835,9 +18835,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18940,9 +18940,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19465,9 +19465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19675,9 +19675,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19745,9 +19745,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19920,9 +19920,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20165,9 +20165,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20340,9 +20340,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20480,9 +20480,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20515,9 +20515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20655,9 +20655,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20690,9 +20690,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20725,9 +20725,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20865,9 +20865,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20935,9 +20935,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20970,9 +20970,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21040,9 +21040,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21075,9 +21075,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21110,9 +21110,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21250,9 +21250,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21763,9 +21763,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21798,9 +21798,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21938,9 +21938,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22113,9 +22113,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22218,9 +22218,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22288,9 +22288,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22533,9 +22533,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22568,9 +22568,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22603,9 +22603,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22638,9 +22638,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22673,9 +22673,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22708,9 +22708,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22743,9 +22743,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22848,9 +22848,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22918,9 +22918,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22953,9 +22953,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22988,9 +22988,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23023,9 +23023,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23058,9 +23058,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23093,9 +23093,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23128,9 +23128,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23163,9 +23163,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23198,9 +23198,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23233,9 +23233,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23268,9 +23268,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23303,9 +23303,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23338,9 +23338,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23373,9 +23373,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23408,9 +23408,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23443,9 +23443,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23478,9 +23478,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23513,9 +23513,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23548,9 +23548,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23583,9 +23583,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23618,9 +23618,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23653,9 +23653,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23688,9 +23688,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23723,9 +23723,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23758,9 +23758,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23793,9 +23793,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23828,9 +23828,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23863,9 +23863,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23898,9 +23898,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23933,9 +23933,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23968,9 +23968,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24003,9 +24003,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24038,9 +24038,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24073,9 +24073,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24108,9 +24108,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24143,9 +24143,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24178,9 +24178,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>56</v>
+        <v>439</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.007330802461055112</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>383</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.05013745254614478</v>
+        <v>0.0574682550071999</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14682,9 +14664,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15242,9 +15224,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15382,9 +15364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20270,9 +20252,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20620,9 +20602,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22778,9 +22760,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22883,9 +22865,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,21 +781,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>439</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0574682550071999</v>
+        <v>0.01714884147139678</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.04031941353580312</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14664,9 +14682,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15224,9 +15242,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15364,9 +15382,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16309,9 +16327,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17149,9 +17167,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18012,9 +18030,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18257,9 +18275,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18572,9 +18590,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18817,9 +18835,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19657,9 +19675,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20252,9 +20270,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20602,9 +20620,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22760,9 +22778,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22865,9 +22883,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>131</v>
+        <v>439</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01714884147139678</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>308</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.04031941353580312</v>
+        <v>0.0574682550071999</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14682,9 +14664,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15242,9 +15224,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15382,9 +15364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16327,9 +16309,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17167,9 +17149,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18030,9 +18012,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18590,9 +18572,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18835,9 +18817,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19675,9 +19657,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20270,9 +20252,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20620,9 +20602,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22778,9 +22760,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22883,9 +22865,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,13 +674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>&lt;$200</t>
+          <t>&lt;$199</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -770,31 +770,49 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$200-$650</t>
+          <t>$200-$499</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.010603482131169</v>
+        <v>0.006152637779814112</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>$500-$649</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.004450844351354889</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>≥$650</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>439</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.0574682550071999</v>
       </c>
     </row>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1565,42 +1583,42 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Orlando International Airport</t>
+          <t>InterContinental Toronto Centre by IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>891781</v>
+        <v>797429</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>526.9400000000001</v>
+        <v>294.39</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.01670028852375191</v>
+        <v>0.1666305087976484</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>590.8849818509254</v>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>369.1739327262991</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -1615,12 +1633,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Rosen Centre Hotel</t>
+          <t>Universal´s Endless Summer Resort - Surfside Inn and Suites</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1634,23 +1652,23 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>797825</v>
+        <v>755659</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>514.95</v>
+        <v>198</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.08823488860339047</v>
+        <v>0.003854913393475099</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>645.4422962429105</v>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>262.0229495050016</v>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1665,47 +1683,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>InterContinental Toronto Centre by IHG</t>
+          <t>Hyatt Regency Huntington Beach Resort and Spa</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>Huntington Beach Area</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>797429</v>
+        <v>669802</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>294.39</v>
+        <v>-495.22</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>0.1666305087976484</v>
+        <v>0.0121946485677857</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>369.1739327262991</v>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1715,47 +1733,47 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Universal´s Endless Summer Resort - Surfside Inn and Suites</t>
+          <t>Occidental Tucancun</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>755659</v>
+        <v>614329</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>198</v>
+        <v>-2597.84</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>0.003854913393475099</v>
+        <v>0.1451062866965421</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>262.0229495050016</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1783,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Huntington Beach Resort and Spa</t>
+          <t>Hyatt Place New York Midtown South</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1780,20 +1798,20 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Huntington Beach Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>669802</v>
+        <v>604287</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>-495.22</v>
+        <v>-4090.26</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.0121946485677857</v>
+        <v>0.01700516476442485</v>
       </c>
       <c r="J23" s="13" t="n">
         <v>0</v>
@@ -1815,12 +1833,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Occidental Tucancun</t>
+          <t>Camino Real Polanco México</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1830,27 +1848,27 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>614329</v>
+        <v>603438</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>-2597.84</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>0.1451062866965421</v>
+        <v>0.01686834438666441</v>
       </c>
       <c r="J24" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -1865,42 +1883,42 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Place New York Midtown South</t>
+          <t>Majestic Elegance Punta Cana - All Inclusive</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>604287</v>
+        <v>597392</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-4090.26</v>
+        <v>-390.39</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.01700516476442485</v>
+        <v>0.03228365964057101</v>
       </c>
       <c r="J25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1915,12 +1933,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Camino Real Polanco México</t>
+          <t>Sunset Royal Beach Resort - All Inclusive</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1930,20 +1948,20 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>603438</v>
+        <v>590582</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0</v>
+        <v>-11.5</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0.01686834438666441</v>
+        <v>0.001390154119157035</v>
       </c>
       <c r="J26" s="13" t="n">
         <v>0</v>
@@ -1965,7 +1983,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Majestic Elegance Punta Cana - All Inclusive</t>
+          <t>Rosita Malecón Centro y Playa</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1975,37 +1993,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>597392</v>
+        <v>580422</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>-390.39</v>
+        <v>165.91</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.03228365964057101</v>
+        <v>0.01409147137772173</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>285.8437481694353</v>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2015,35 +2033,35 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Sunset Royal Beach Resort - All Inclusive</t>
+          <t>Disney's Caribbean Beach Resort</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>590582</v>
+        <v>575486</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>-11.5</v>
+        <v>-15.28999999999997</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.001390154119157035</v>
+        <v>0.01215146849793045</v>
       </c>
       <c r="J28" s="13" t="n">
         <v>0</v>
@@ -2065,7 +2083,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Rosita Malecón Centro y Playa</t>
+          <t>Casa de Campo Resort and Villas</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2075,37 +2093,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>La Romana Area</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>580422</v>
+        <v>575390</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>165.91</v>
+        <v>29.16000000000003</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.01409147137772173</v>
+        <v>0.02376475086463094</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>285.8437481694353</v>
+        <v>50.67867011939733</v>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2133,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Disney's Caribbean Beach Resort</t>
+          <t>Silver Legacy Reno - A Caesars Rewards Destination</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2130,32 +2148,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Reno Area</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>575486</v>
+        <v>571475</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>-15.28999999999997</v>
+        <v>253.69</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.01215146849793045</v>
+        <v>0.04411916531781793</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>443.9214313837001</v>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2165,38 +2183,38 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Casa de Campo Resort and Villas</t>
+          <t>Casa Marina Key West, Curio Collection by Hilton</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>La Romana Area</t>
+          <t>Key West Area</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>575390</v>
+        <v>571303</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>29.16000000000003</v>
+        <v>-19333.83</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.02376475086463094</v>
+        <v>0.00376157660645927</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>50.67867011939733</v>
+        <v>0</v>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
@@ -2215,47 +2233,47 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Silver Legacy Reno - A Caesars Rewards Destination</t>
+          <t>Ocean El Faro</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Reno Area</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>571475</v>
+        <v>563685</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>253.69</v>
+        <v>-2498.19</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>0.04411916531781793</v>
+        <v>0.01983732048928036</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>443.9214313837001</v>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2265,35 +2283,35 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Casa Marina Key West, Curio Collection by Hilton</t>
+          <t>Holiday Inn Resort Aruba</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Key West Area</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>571303</v>
+        <v>556884</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-19333.83</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.00376157660645927</v>
+        <v>0.01406037882216045</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>0</v>
@@ -2315,35 +2333,35 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Ocean El Faro</t>
+          <t>Ramada by Wyndham Miami Springs/Miami International Airport</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>563685</v>
+        <v>538224</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>-2498.19</v>
+        <v>0</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>0.01983732048928036</v>
+        <v>0.002589999702726003</v>
       </c>
       <c r="J34" s="13" t="n">
         <v>0</v>
@@ -2365,47 +2383,47 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Resort Aruba</t>
+          <t>Canto del Sol Puerto Vallarta All Inclusive</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>556884</v>
+        <v>537317</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0</v>
+        <v>264.36</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.01406037882216045</v>
+        <v>0.01970531362305678</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>0</v>
+        <v>492.0000669995553</v>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2415,35 +2433,35 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Ramada by Wyndham Miami Springs/Miami International Airport</t>
+          <t>Princess Mundo Imperial Riviera Diamante Acapulco</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Acapulco</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>538224</v>
+        <v>528062</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0</v>
+        <v>-118.6</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>0.002589999702726003</v>
+        <v>0.01290757524684602</v>
       </c>
       <c r="J36" s="13" t="n">
         <v>0</v>
@@ -2465,47 +2483,47 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Canto del Sol Puerto Vallarta All Inclusive</t>
+          <t>Quality Inn &amp; Suites - Toronto West</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>537317</v>
+        <v>520310</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>264.36</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.01970531362305678</v>
+        <v>0.01187561261555611</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>492.0000669995553</v>
+        <v>178.8741327285657</v>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2533,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Princess Mundo Imperial Riviera Diamante Acapulco</t>
+          <t>Plaza Pelícanos Club Beach Resort</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2530,32 +2548,32 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Acapulco</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>528062</v>
+        <v>515826</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>-118.6</v>
+        <v>117.37</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>0.01290757524684602</v>
+        <v>0.0260960091193542</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0</v>
+        <v>227.5379682295968</v>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2565,38 +2583,38 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Quality Inn &amp; Suites - Toronto West</t>
+          <t>Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>520310</v>
+        <v>514925</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>93.06999999999999</v>
+        <v>-281.06</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0.01187561261555611</v>
+        <v>0.01333786473758314</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>178.8741327285657</v>
+        <v>0</v>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
@@ -2615,47 +2633,47 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Plaza Pelícanos Club Beach Resort</t>
+          <t>Excalibur Hotel &amp; Casino</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>515826</v>
+        <v>509964</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>117.37</v>
+        <v>-151.16</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>0.0260960091193542</v>
+        <v>0.01502262904832498</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>227.5379682295968</v>
+        <v>0</v>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2665,35 +2683,35 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
+          <t>Hyatt Regency Milwaukee</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Riviera Nayarit</t>
+          <t>Milwaukee Area</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>514925</v>
+        <v>509124</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>-281.06</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.01333786473758314</v>
+        <v>0.008716933399329043</v>
       </c>
       <c r="J41" s="13" t="n">
         <v>0</v>
@@ -2715,12 +2733,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Excalibur Hotel &amp; Casino</t>
+          <t>Disney's Port Orleans Resort - French Quarter</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2730,20 +2748,20 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>509964</v>
+        <v>499394</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>-151.16</v>
+        <v>-781.67</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>0.01502262904832498</v>
+        <v>0.009275241592810487</v>
       </c>
       <c r="J42" s="13" t="n">
         <v>0</v>
@@ -2765,38 +2783,38 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Milwaukee</t>
+          <t>Hotel Imperial Reforma</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Milwaukee Area</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>509124</v>
+        <v>498148</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0</v>
+        <v>49.59</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.008716933399329043</v>
+        <v>0.01604342484562821</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0</v>
+        <v>99.54872849032817</v>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
@@ -2815,12 +2833,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Disney's Port Orleans Resort - French Quarter</t>
+          <t>Luxor Hotel and Casino</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2830,27 +2848,27 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>499394</v>
+        <v>496224</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>-781.67</v>
+        <v>-551.0699999999999</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>0.009275241592810487</v>
+        <v>0.03284605339524086</v>
       </c>
       <c r="J44" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -2865,12 +2883,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Hotel Imperial Reforma</t>
+          <t>AVA Resort Cancun</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2880,23 +2898,23 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>498148</v>
+        <v>485118</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>49.59</v>
+        <v>-2083.14</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.01604342484562821</v>
+        <v>0.005763546188762321</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>99.54872849032817</v>
+        <v>0</v>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
@@ -2915,35 +2933,35 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Luxor Hotel and Casino</t>
+          <t>Ocean Coral Spring Resort - All inclusive</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>496224</v>
+        <v>484460</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-551.0699999999999</v>
+        <v>-1704.59</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>0.03284605339524086</v>
+        <v>0.03364364447013169</v>
       </c>
       <c r="J46" s="13" t="n">
         <v>0</v>
@@ -2965,12 +2983,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>AVA Resort Cancun</t>
+          <t>Dreams Natura Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2980,20 +2998,20 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>485118</v>
+        <v>459452</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>-2083.14</v>
+        <v>-3060</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.005763546188762321</v>
+        <v>0.01589284626032752</v>
       </c>
       <c r="J47" s="13" t="n">
         <v>0</v>
@@ -3015,42 +3033,42 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Ocean Coral Spring Resort - All inclusive</t>
+          <t>Secrets Tulum Resort &amp; Beach Club - All Inclusive - Adults Only</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>484460</v>
+        <v>447712</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>-1704.59</v>
+        <v>0</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.03364364447013169</v>
+        <v>0.005034486455578586</v>
       </c>
       <c r="J48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -3065,12 +3083,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Catalonia Grand Costa Mujeres All Suites &amp; Spa - Todo Incluido</t>
+          <t>Hard Rock Hotel Vallarta</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3080,32 +3098,32 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>470571</v>
+        <v>440347</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>258.32</v>
+        <v>-3636.92</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.02819128250572177</v>
+        <v>0.158172986303983</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>548.9501052976066</v>
-      </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3133,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Dreams Natura Resort &amp; Spa</t>
+          <t>Renaissance Cancun Resort &amp; Marina</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3130,32 +3148,32 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>459452</v>
+        <v>435612</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>-3060</v>
+        <v>148.07</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>0.01589284626032752</v>
+        <v>0.003578872941975887</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0</v>
+        <v>339.9125827571325</v>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3183,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Secrets Tulum Resort &amp; Beach Club - All Inclusive - Adults Only</t>
+          <t>Tesoro Ixtapa All Inclusive</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3180,20 +3198,20 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>447712</v>
+        <v>435552</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0</v>
+        <v>-387.12</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>0.005034486455578586</v>
+        <v>0.002713797663654397</v>
       </c>
       <c r="J51" s="13" t="n">
         <v>0</v>
@@ -3215,47 +3233,47 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock Hotel Vallarta</t>
+          <t>Radisson Hotel Montreal Airport</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Riviera Nayarit</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>440347</v>
+        <v>431368</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>-3636.92</v>
+        <v>107.05</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>0.158172986303983</v>
+        <v>0.1543670369614807</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>0</v>
+        <v>248.1639806383413</v>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3283,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Renaissance Cancun Resort &amp; Marina</t>
+          <t>Banyan Tree Mayakoba</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3280,32 +3298,32 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>435612</v>
+        <v>430257</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>148.07</v>
+        <v>-433.77</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.003578872941975887</v>
+        <v>0.03915566742667755</v>
       </c>
       <c r="J53" s="13" t="n">
-        <v>339.9125827571325</v>
-      </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3333,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Tesoro Ixtapa All Inclusive</t>
+          <t>Hotel Sevilla</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3330,32 +3348,32 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Ixtapa / Zihuatanejo</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>435552</v>
+        <v>423114</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>-387.12</v>
+        <v>125.65</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>0.002713797663654397</v>
+        <v>0.004963201406713085</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>0</v>
+        <v>296.9648841683329</v>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3365,47 +3383,47 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Radisson Hotel Montreal Airport</t>
+          <t>Ocean Riviera Paradise - All Inclusive</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>431368</v>
+        <v>421669</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>107.05</v>
+        <v>-1403.24</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.1543670369614807</v>
+        <v>0.01047741237795522</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>248.1639806383413</v>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3415,47 +3433,47 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Banyan Tree Mayakoba</t>
+          <t>Best Western Fort Myers Inn &amp; Suites</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Fort Myers Area</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>430257</v>
+        <v>416334</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>-433.77</v>
+        <v>87.38</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>0.03915566742667755</v>
+        <v>0.001618892523790995</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>209.879567846969</v>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3465,47 +3483,47 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Hotel Sevilla</t>
+          <t>Hyatt Regency Los Angeles International Airport</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>423114</v>
+        <v>404040</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>125.65</v>
+        <v>0</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>0.004963201406713085</v>
+        <v>0.02480694980694981</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>296.9648841683329</v>
+        <v>0</v>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3533,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Ocean Riviera Paradise - All Inclusive</t>
+          <t>Unico Hotel Riviera Maya Adults Only</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3534,16 +3552,16 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>421669</v>
+        <v>402294</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>-1403.24</v>
+        <v>-3432.71</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>0.01047741237795522</v>
+        <v>0.007188772390341392</v>
       </c>
       <c r="J58" s="13" t="n">
         <v>0</v>
@@ -3565,12 +3583,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Best Western Fort Myers Inn &amp; Suites</t>
+          <t>ARIA Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3580,32 +3598,32 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Fort Myers Area</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>416334</v>
+        <v>395671</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>87.38</v>
+        <v>-615.05</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.001618892523790995</v>
+        <v>0.01885404793376315</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>209.879567846969</v>
+        <v>0</v>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3633,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Hotel Monterrey Macroplaza</t>
+          <t>BlueBay Grand Esmeralda</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3630,32 +3648,32 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>410772</v>
+        <v>390333</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>258.53</v>
+        <v>-691.5</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>0.0196727138169106</v>
+        <v>0.02998209221357149</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>629.3759068290924</v>
+        <v>0</v>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3665,47 +3683,47 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Safi Royal Luxury Valle</t>
+          <t>Sofitel Legend Santa Clara Cartagena</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>410689</v>
+        <v>374625</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>249.89</v>
+        <v>-200.6799999999999</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>0.0124692894136439</v>
+        <v>0.001505505505505506</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>608.4652863845878</v>
+        <v>0</v>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3715,35 +3733,35 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Los Angeles International Airport</t>
+          <t>Royal Decameron Salinitas - All Inclusive</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Decameron</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>El Salvador Area</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>404040</v>
+        <v>371131</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>0.02480694980694981</v>
+        <v>0.01580573975227076</v>
       </c>
       <c r="J62" s="13" t="n">
         <v>0</v>
@@ -3765,12 +3783,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Unico Hotel Riviera Maya Adults Only</t>
+          <t>Holiday Inn Express Mexico Aeropuerto, an IHG Hotel</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3780,20 +3798,20 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>402294</v>
+        <v>363363</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>-3432.71</v>
+        <v>-121.61</v>
       </c>
       <c r="I63" s="14" t="n">
-        <v>0.007188772390341392</v>
+        <v>0.00265574645739935</v>
       </c>
       <c r="J63" s="13" t="n">
         <v>0</v>
@@ -3815,12 +3833,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>ARIA Resort &amp; Casino</t>
+          <t>Peppermill Resort Spa Casino</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3830,27 +3848,27 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Reno Area</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>395671</v>
+        <v>361024</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>-615.05</v>
+        <v>-539.47</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>0.01885404793376315</v>
+        <v>0.5065868197128168</v>
       </c>
       <c r="J64" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -3865,47 +3883,47 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>BlueBay Grand Esmeralda</t>
+          <t>Best Western Plus Miami Airport North Hotel &amp; Suites</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>390333</v>
+        <v>359209</v>
       </c>
       <c r="G65" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>-691.5</v>
+        <v>100.57</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.02998209221357149</v>
+        <v>0.001311214362669087</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>0</v>
+        <v>279.9762812178982</v>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3915,47 +3933,47 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Sofitel Legend Santa Clara Cartagena</t>
+          <t>Hyatt Place Fort Worth/Hurst</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Fort Worth Area</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>374625</v>
+        <v>356189</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>-200.6799999999999</v>
+        <v>99.13</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>0.001505505505505506</v>
+        <v>0.004202824904755621</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>0</v>
+        <v>278.3073031452403</v>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3965,35 +3983,35 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Royal Decameron Salinitas - All Inclusive</t>
+          <t>Crown Paradise Golden All Inclusive Resort, Adults Only</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Decameron</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>El Salvador Area</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>371131</v>
+        <v>354495</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>0</v>
+        <v>-132.11</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>0.01580573975227076</v>
+        <v>0.01045995006981763</v>
       </c>
       <c r="J67" s="13" t="n">
         <v>0</v>
@@ -4015,12 +4033,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Express Mexico Aeropuerto, an IHG Hotel</t>
+          <t>Hotel Castillo Huatulco &amp; Beach Club</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4030,27 +4048,27 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Huatulco Area</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>363363</v>
+        <v>350558</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>-121.61</v>
+        <v>-136.64</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>0.00265574645739935</v>
+        <v>0.03026032782021805</v>
       </c>
       <c r="J68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -4065,42 +4083,42 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Peppermill Resort Spa Casino</t>
+          <t>Bahia Principe Escape Aquamarine</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Reno Area</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>361024</v>
+        <v>350080</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>-539.47</v>
+        <v>0</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0.5065868197128168</v>
+        <v>0.01213436928702011</v>
       </c>
       <c r="J69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4115,12 +4133,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Best Western Plus Miami Airport North Hotel &amp; Suites</t>
+          <t>Holiday Inn Resort Kissimmee by the Parks</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4130,32 +4148,32 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>359209</v>
+        <v>349036</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>100.57</v>
+        <v>-624.26</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>0.001311214362669087</v>
+        <v>0.009265519889065885</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>279.9762812178982</v>
+        <v>0</v>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4165,47 +4183,47 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Place Fort Worth/Hurst</t>
+          <t>Hotel Dorado la 70</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Fort Worth Area</t>
+          <t>Medellin Area</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>356189</v>
+        <v>343719</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>99.13</v>
+        <v>-498.86</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>0.004202824904755621</v>
+        <v>0.001847439332710732</v>
       </c>
       <c r="J71" s="13" t="n">
-        <v>278.3073031452403</v>
+        <v>0</v>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L71" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4233,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Crown Paradise Golden All Inclusive Resort, Adults Only</t>
+          <t>Comfort Inn Cancún Aeropuerto</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4230,32 +4248,32 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>354495</v>
+        <v>343346</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>-132.11</v>
+        <v>146.77</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>0.01045995006981763</v>
+        <v>0.01140831697471355</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>0</v>
+        <v>427.469666167656</v>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4283,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Hotel Castillo Huatulco &amp; Beach Club</t>
+          <t>Hotel Ashly</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -4280,32 +4298,32 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Huatulco Area</t>
+          <t>Acapulco</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>350558</v>
+        <v>341793</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>-136.64</v>
+        <v>99.83</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0.03026032782021805</v>
+        <v>0.001761299968109353</v>
       </c>
       <c r="J73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>292.0773684657087</v>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4315,42 +4333,42 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe Escape Aquamarine</t>
+          <t>Las Américas Golden Tower Panamá</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>Americas Hotels Group</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Panama City Area</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>350080</v>
+        <v>339523</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="14" t="n">
-        <v>0.01213436928702011</v>
+        <v>0.04080430486299897</v>
       </c>
       <c r="J74" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -4365,35 +4383,35 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Resort Kissimmee by the Parks</t>
+          <t>Bahia Principe Explore La Romana</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>La Romana Area</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>349036</v>
+        <v>327206</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>-624.26</v>
+        <v>0</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.009265519889065885</v>
+        <v>0.02188529550191622</v>
       </c>
       <c r="J75" s="13" t="n">
         <v>0</v>
@@ -4415,47 +4433,47 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Hotel Bristol</t>
+          <t>DoubleTree Suites by Hilton Anaheim Rsrt - Conv Cntr</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>347847</v>
+        <v>323829</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>0.005444922624027231</v>
+        <v>0.005271300593831929</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>540.7549871064002</v>
+        <v>0</v>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4483,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Hotel Dorado la 70</t>
+          <t>GHL Relax Corales de Indias</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4480,20 +4498,20 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Medellin Area</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>343719</v>
+        <v>320026</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-498.86</v>
+        <v>0</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.001847439332710732</v>
+        <v>0.004727740871054227</v>
       </c>
       <c r="J77" s="13" t="n">
         <v>0</v>
@@ -4515,47 +4533,47 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Comfort Inn Cancún Aeropuerto</t>
+          <t>Binn Hotel</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Medellin Area</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>343346</v>
+        <v>318759</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>146.77</v>
+        <v>-382.8</v>
       </c>
       <c r="I78" s="14" t="n">
-        <v>0.01140831697471355</v>
+        <v>0.02228956672595911</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>427.469666167656</v>
+        <v>0</v>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4583,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Hotel Ashly</t>
+          <t>Palacio Mundo Imperial Riviera Diamante Acapulco</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4584,28 +4602,28 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>341793</v>
+        <v>318585</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>99.83</v>
+        <v>-257.25</v>
       </c>
       <c r="I79" s="14" t="n">
-        <v>0.001761299968109353</v>
+        <v>0.01986910871509958</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>292.0773684657087</v>
+        <v>0</v>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4615,42 +4633,42 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Las Américas Golden Tower Panamá</t>
+          <t>Grand Hyatt San Francisco</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Americas Hotels Group</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Panama City Area</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>339523</v>
+        <v>316553</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>0</v>
+        <v>6.950000000000046</v>
       </c>
       <c r="I80" s="14" t="n">
-        <v>0.04080430486299897</v>
+        <v>0.01904578380239644</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>21.95524919997614</v>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -4665,12 +4683,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Hotel Madero Express</t>
+          <t>Hyatt Zilara Riviera Maya</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4680,32 +4698,32 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>331085</v>
+        <v>313617</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>170.2</v>
+        <v>-918</v>
       </c>
       <c r="I81" s="14" t="n">
-        <v>0.0228793210202818</v>
+        <v>0.2119049668863614</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>514.0673845085099</v>
-      </c>
-      <c r="K81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4733,35 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe Explore La Romana</t>
+          <t>Playa Blanca All Inclusive Beach Resort Panama</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>La Romana Area</t>
+          <t>Playas Pacífico Panamá Area</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>327206</v>
+        <v>313232</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>0</v>
+        <v>-266.19</v>
       </c>
       <c r="I82" s="14" t="n">
-        <v>0.02188529550191622</v>
+        <v>0.01189533636410073</v>
       </c>
       <c r="J82" s="13" t="n">
         <v>0</v>
@@ -4765,47 +4783,47 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree Suites by Hilton Anaheim Rsrt - Conv Cntr</t>
+          <t>Extended Suites Mexicali Cataviña</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>323829</v>
+        <v>311674</v>
       </c>
       <c r="G83" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>0</v>
+        <v>71.61</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.005271300593831929</v>
+        <v>0.002412777453364734</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>0</v>
+        <v>229.7592997811816</v>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4815,47 +4833,47 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>GHL Relax Corales de Indias</t>
+          <t>Hotel La Venta Inn Villahermosa</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>320026</v>
+        <v>306955</v>
       </c>
       <c r="G84" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>0</v>
+        <v>124.21</v>
       </c>
       <c r="I84" s="14" t="n">
-        <v>0.004727740871054227</v>
+        <v>0.005333029271391572</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>0</v>
+        <v>404.6521477089476</v>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4865,38 +4883,38 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Binn Hotel</t>
+          <t>Hotel Misión Monterrey Centro Histórico</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Medellin Area</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>318759</v>
+        <v>306366</v>
       </c>
       <c r="G85" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="13" t="n">
-        <v>-382.8</v>
+        <v>2.579999999999998</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>0.02228956672595911</v>
+        <v>0.004892840589360438</v>
       </c>
       <c r="J85" s="13" t="n">
-        <v>0</v>
+        <v>8.421300013709086</v>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
@@ -4915,47 +4933,47 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Palacio Mundo Imperial Riviera Diamante Acapulco</t>
+          <t>Hampton Inn &amp; Suites Miami-Airport South-Blue Lagoon</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Acapulco</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>318585</v>
+        <v>303451</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-257.25</v>
+        <v>123.47</v>
       </c>
       <c r="I86" s="14" t="n">
-        <v>0.01986910871509958</v>
+        <v>0.009309575516310706</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>0</v>
+        <v>406.8861199996045</v>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4965,47 +4983,47 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Hampton Inn &amp; Suites Orlando Airport @ Gateway Village</t>
+          <t>Real Bananas ACA - Todo Incluido</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Acapulco</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>317581</v>
+        <v>303388</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>169.68</v>
+        <v>-109.5399999999999</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>0.00425088402643735</v>
+        <v>0.01450617690877688</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>534.2888900784367</v>
+        <v>0</v>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5015,38 +5033,38 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Grand Hyatt San Francisco</t>
+          <t>Ambiance Suites</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>316553</v>
+        <v>302482</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>6.950000000000046</v>
+        <v>0</v>
       </c>
       <c r="I88" s="14" t="n">
-        <v>0.01904578380239644</v>
+        <v>0.006585515832347049</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>21.95524919997614</v>
+        <v>0</v>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
@@ -5065,12 +5083,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Zilara Riviera Maya</t>
+          <t>Container Inn Hotel Aeropuerto</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -5080,32 +5098,32 @@
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>313617</v>
+        <v>295367</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>-918</v>
+        <v>100.37</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>0.2119049668863614</v>
+        <v>0.002593383824191599</v>
       </c>
       <c r="J89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>339.8145358147661</v>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5115,42 +5133,42 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Playa Blanca All Inclusive Beach Resort Panama</t>
+          <t>El Dorado Royale, All &amp; More Inclusive Adults Only</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Lomas Hospitality</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Playas Pacífico Panamá Area</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>313232</v>
+        <v>295139</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-266.19</v>
+        <v>-152.24</v>
       </c>
       <c r="I90" s="14" t="n">
-        <v>0.01189533636410073</v>
+        <v>0.04830266416840878</v>
       </c>
       <c r="J90" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K90" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -5165,12 +5183,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Extended Suites Mexicali Cataviña</t>
+          <t>Hyatt Regency Ciudad de Mexico Insurgentes</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5180,32 +5198,32 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Baja California</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>311674</v>
+        <v>293897</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>71.61</v>
+        <v>-358.51</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>0.002412777453364734</v>
+        <v>0.005651639860223139</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>229.7592997811816</v>
+        <v>0</v>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L91" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5233,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Hotel La Venta Inn Villahermosa</t>
+          <t>Club Regina Los Cabos</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Park Royal</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5230,32 +5248,32 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Los Cabos Area</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>306955</v>
+        <v>291843</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>124.21</v>
+        <v>-162.47</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>0.005333029271391572</v>
+        <v>0.0038411063482763</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>404.6521477089476</v>
+        <v>0</v>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L92" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5265,42 +5283,42 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Hotel Misión Monterrey Centro Histórico</t>
+          <t>Oz Hotel Luxury</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>306366</v>
+        <v>291268</v>
       </c>
       <c r="G93" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>2.579999999999998</v>
+        <v>-565.46</v>
       </c>
       <c r="I93" s="14" t="n">
-        <v>0.004892840589360438</v>
+        <v>0.07963799662166801</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>8.421300013709086</v>
-      </c>
-      <c r="K93" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5315,47 +5333,47 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Hampton Inn &amp; Suites Miami-Airport South-Blue Lagoon</t>
+          <t>The Westin Cozumel</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Cozumel</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>303451</v>
+        <v>288015</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>123.47</v>
+        <v>0</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>0.009309575516310706</v>
+        <v>0.003131781330833464</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>406.8861199996045</v>
+        <v>0</v>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L94" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5383,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Real Bananas ACA - Todo Incluido</t>
+          <t>Hotel Stadium</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -5380,32 +5398,32 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Acapulco</t>
+          <t>León</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>303388</v>
+        <v>279669</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>-109.5399999999999</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>0.01450617690877688</v>
+        <v>0.01326568193114003</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>0</v>
+        <v>311.1177856680576</v>
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5415,26 +5433,26 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Ambiance Suites</t>
+          <t>Athens Capital Center Hotel-MGallery Collection</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>302482</v>
+        <v>278135</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>2</v>
@@ -5443,14 +5461,14 @@
         <v>0</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>0.006585515832347049</v>
+        <v>0.0666726589605767</v>
       </c>
       <c r="J96" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -5465,12 +5483,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Container Inn Hotel Aeropuerto</t>
+          <t>Wyndham Garden Guadalajara Expo</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -5480,23 +5498,23 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>295367</v>
+        <v>278008</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>100.37</v>
+        <v>87.52</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>0.002593383824191599</v>
+        <v>0.001629449512244252</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>339.8145358147661</v>
+        <v>314.8110845731058</v>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
@@ -5515,12 +5533,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>El Dorado Royale, All &amp; More Inclusive Adults Only</t>
+          <t>Nílu Puerto Escondido by Selina</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Lomas Hospitality</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -5530,23 +5548,23 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Puerto Escondido Area</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>295139</v>
+        <v>274475</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-152.24</v>
+        <v>3.780000000000001</v>
       </c>
       <c r="I98" s="14" t="n">
-        <v>0.04830266416840878</v>
+        <v>0.03738045359322343</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>0</v>
+        <v>13.77174606066127</v>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
@@ -5565,47 +5583,47 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Ciudad de Mexico Insurgentes</t>
+          <t>Sonesta Hotel Pereira</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Eje cafetero</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>293897</v>
+        <v>271020</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-358.51</v>
+        <v>115.54</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>0.005651639860223139</v>
+        <v>0.009471625710279685</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>0</v>
+        <v>426.3154010774113</v>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5615,12 +5633,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Club Regina Los Cabos</t>
+          <t>Fiesta Inn Cancún Las Américas</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Park Royal</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -5630,20 +5648,20 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Los Cabos Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>291843</v>
+        <v>265901</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>-162.47</v>
+        <v>-107.73</v>
       </c>
       <c r="I100" s="14" t="n">
-        <v>0.0038411063482763</v>
+        <v>0.01966521374496523</v>
       </c>
       <c r="J100" s="13" t="n">
         <v>0</v>
@@ -5665,7 +5683,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Oz Hotel Luxury</t>
+          <t>Hotel Costa del Sol</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5684,19 +5702,19 @@
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>291268</v>
+        <v>257954</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>-565.46</v>
+        <v>38.84</v>
       </c>
       <c r="I101" s="14" t="n">
-        <v>0.07963799662166801</v>
+        <v>0.08516247082813215</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>0</v>
+        <v>150.5694813804012</v>
       </c>
       <c r="K101" s="8" t="inlineStr">
         <is>
@@ -5715,47 +5733,47 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Homewood Suites by Hilton Nashville Vanderbilt, TN</t>
+          <t>Hotel Calypso Cancún</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Nashville (and vicinity), TN, US</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>290176</v>
+        <v>254708</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>176.85</v>
+        <v>-476.1</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>0.001647276135862373</v>
+        <v>0.1176798530081505</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>609.4577084252315</v>
-      </c>
-      <c r="K102" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5783,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>The Westin Cozumel</t>
+          <t>Bacalar102</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -5780,23 +5798,23 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Cozumel</t>
+          <t>Bacalar Area</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>288015</v>
+        <v>253283</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H103" s="13" t="n">
-        <v>0</v>
+        <v>22.71</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>0.003131781330833464</v>
+        <v>0.001247616302712776</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>0</v>
+        <v>89.66255137533905</v>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
@@ -5815,47 +5833,47 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Hotel El Prado</t>
+          <t>Hotel Mision Toreo Centro de Convenciones</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Barranquilla Area</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>281246</v>
+        <v>249264</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>178</v>
+        <v>-126.68</v>
       </c>
       <c r="I104" s="14" t="n">
-        <v>0.01668290393463374</v>
+        <v>0.009732652930226586</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>632.8978901033259</v>
+        <v>0</v>
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L104" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5883,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Hotel Mision Puebla Angelopolis</t>
+          <t>Wyndham Puebla Angelopolis</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5884,28 +5902,28 @@
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>280683</v>
+        <v>248769</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" s="13" t="n">
-        <v>166.47</v>
+        <v>-104.47</v>
       </c>
       <c r="I105" s="14" t="n">
-        <v>0.003245654350281278</v>
+        <v>0.001873223753763531</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>593.0890007588632</v>
+        <v>0</v>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L105" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15924,9 +15942,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16064,9 +16082,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16694,9 +16712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17907,9 +17925,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18607,9 +18625,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18992,9 +19010,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19587,9 +19605,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20042,9 +20060,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20077,9 +20095,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20217,9 +20235,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20532,9 +20550,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21465,9 +21483,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22445,9 +22463,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -527,7 +527,7 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.002487236549286556</v>
+        <v>0.001803968731208659</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02565780861369289</v>
+        <v>0.02685908999799559</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1072</v>
+        <v>680</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1403325042544836</v>
+        <v>0.1362998596913209</v>
       </c>
     </row>
     <row r="9">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>680</v>
+        <v>433</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.08901688702709779</v>
+        <v>0.08679094006814993</v>
       </c>
     </row>
     <row r="10">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5672</v>
+        <v>3733</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7425055635554392</v>
+        <v>0.748246141511325</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6954</v>
+        <v>4412</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.9103285770388795</v>
+        <v>0.8843455602325115</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02159968582275167</v>
+        <v>0.03046702746041291</v>
       </c>
     </row>
     <row r="8">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.006152637779814112</v>
+        <v>0.009019843656043296</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.004450844351354889</v>
+        <v>0.006814992984566046</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>439</v>
+        <v>346</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.0574682550071999</v>
+        <v>0.06935257566646623</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14536,15 +14536,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14628,19 +14628,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>304928875</v>
+        <v>270333990</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1136.779999999997</v>
+        <v>-6351.56</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.01859722861601742</v>
+        <v>0.01786797879171613</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>3.728016902302209</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -14663,19 +14663,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>210328009</v>
+        <v>187181665</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>968</v>
+        <v>913</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>143952.54</v>
+        <v>135982.7</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.03723196942353027</v>
+        <v>0.03823596183953167</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>684.4192586827559</v>
+        <v>726.4744653275736</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -14694,32 +14694,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>194667038</v>
+        <v>153859733</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>11035.45</v>
+        <v>41615.89</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.02292827304435587</v>
+        <v>0.02373299971864633</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>56.68884734353435</v>
+        <v>270.4794112700039</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14729,32 +14729,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>160555474</v>
+        <v>148627056</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>43923.28</v>
+        <v>9754.799999999999</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.02426952443863733</v>
+        <v>0.02427524366761325</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>273.5707410387017</v>
+        <v>65.63273378704345</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14768,19 +14768,19 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>77395523</v>
+        <v>68173517</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>25646.73</v>
+        <v>24720.81</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.08343531705315824</v>
+        <v>0.08257889936938416</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>331.3722681349411</v>
+        <v>362.6160287432435</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -14803,28 +14803,28 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>69717558</v>
+        <v>57515009</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>14339.91</v>
+        <v>8035.380000000001</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.01718152549175632</v>
+        <v>0.01698829604634157</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>205.6857757410264</v>
+        <v>139.7092713660186</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14838,19 +14838,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>26555231</v>
+        <v>24983391</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>-2651.01</v>
+        <v>550.63</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.1097514836154127</v>
+        <v>0.1097884990872536</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0</v>
+        <v>22.03984238969001</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
@@ -14869,32 +14869,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>23817671</v>
+        <v>21929081</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>2845.52</v>
+        <v>4748.23</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.04981612181980346</v>
+        <v>0.02071468476038736</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>119.4709591882431</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>216.5266296385152</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14904,32 +14904,32 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>22110259</v>
+        <v>17201082</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>4748.23</v>
+        <v>1663.71</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.02064774546512549</v>
+        <v>0.04517942534080124</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>214.752346410777</v>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>96.72124114052825</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>12190885</v>
+        <v>12067650</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>43</v>
@@ -14952,19 +14952,19 @@
         <v>6064.32</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.02664777823759309</v>
+        <v>0.02622018371431057</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>497.4470680348473</v>
+        <v>502.5270040148661</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14978,19 +14978,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>10714198</v>
+        <v>10398989</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>-158.5099999999999</v>
+        <v>702.59</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.07322563947390183</v>
+        <v>0.0740572953774641</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0</v>
+        <v>67.56329870144108</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -15009,32 +15009,32 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>10606507</v>
+        <v>10262516</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>4399.97</v>
+        <v>-319.33</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.0406953957603573</v>
+        <v>0.1144246693500892</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>414.8368543951369</v>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15044,32 +15044,32 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>10581203</v>
+        <v>8833260</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>1524.109999999999</v>
+        <v>15062.76</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.06796977621542655</v>
+        <v>0.02540534298775311</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>144.0393875819223</v>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1705.232269852807</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15079,32 +15079,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10311631</v>
+        <v>8509015</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>-319.33</v>
+        <v>4399.97</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.1144108046535024</v>
+        <v>0.03230608948274272</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>517.0951044274807</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15114,32 +15114,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>9046707</v>
+        <v>8335677</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>15062.76</v>
+        <v>3006.67</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.02545301842979993</v>
+        <v>0.06501259585754103</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1664.999209104484</v>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>360.6989570253262</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>5896013</v>
+        <v>5722987</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>8</v>
@@ -15162,10 +15162,10 @@
         <v>2557.58</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.03074365677280562</v>
+        <v>0.03101597120524649</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>433.7812687997805</v>
+        <v>446.8960002879616</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -15184,27 +15184,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5509533</v>
+        <v>5492314</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>18730.5</v>
+        <v>4156.64</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.02717816555414043</v>
+        <v>0.04160159087772477</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>3399.6529288417</v>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>756.8103353158615</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -15219,27 +15219,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>5492314</v>
+        <v>5261081</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>4156.64</v>
+        <v>18730.5</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.04160159087772477</v>
+        <v>0.02262975992956581</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>756.8103353158615</v>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>3560.199890478782</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -15258,7 +15258,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>5256047</v>
+        <v>5208423</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>7</v>
@@ -15267,7 +15267,7 @@
         <v>-9596.24</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.04567025370967954</v>
+        <v>0.04601699977133194</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0</v>
@@ -15289,32 +15289,32 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5252167</v>
+        <v>5128474</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>-7.549999999999983</v>
+        <v>1916.17</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.0304811328352659</v>
+        <v>0.01184582392345169</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>373.6335603924286</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15324,32 +15324,32 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>5185371</v>
+        <v>4904638</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>1312.7</v>
+        <v>4334.88</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.01185450375681894</v>
+        <v>0.02411064792141642</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>253.1544994562587</v>
+        <v>883.8328129415464</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15359,32 +15359,32 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>5032897</v>
+        <v>4677947</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>4334.88</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.02693478527376976</v>
+        <v>0.1386922511093007</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>861.3091028884556</v>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15394,32 +15394,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>4887752</v>
+        <v>4580887</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>0</v>
+        <v>-7.549999999999983</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.1360973306337965</v>
+        <v>0.02877630467636508</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15429,27 +15429,27 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Park Royal</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4078371</v>
+        <v>3988957</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>686.37</v>
+        <v>-1212.38</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.019596794896786</v>
+        <v>0.04017215527768286</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>168.2951354842411</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>4075932</v>
+        <v>3962709</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>3</v>
@@ -15477,14 +15477,14 @@
         <v>695.14</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.05707283634761326</v>
+        <v>0.04700900318443772</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>170.5474968669742</v>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>175.4204005391261</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -15499,27 +15499,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>Park Royal</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>4036664</v>
+        <v>3875959</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>-1212.38</v>
+        <v>686.37</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.03984354407500847</v>
+        <v>0.01328084223801129</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>177.0839165223368</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>3962519</v>
+        <v>3832025</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>5</v>
@@ -15547,10 +15547,10 @@
         <v>1355.87</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.03439276884224404</v>
+        <v>0.0345900666096907</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>342.1737536148091</v>
+        <v>353.8259797365622</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>3221043</v>
+        <v>3143015</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>4</v>
@@ -15582,10 +15582,10 @@
         <v>814.0599999999999</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.08647447426190835</v>
+        <v>0.0861758534400886</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>252.7318014692756</v>
+        <v>259.0060817399853</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
@@ -15639,23 +15639,23 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Presidente Intercontinental</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>2991765</v>
+        <v>2949246</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>136.01</v>
+        <v>-3385.57</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.03573475857896593</v>
+        <v>0.03552772471336742</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>45.46145836989201</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -15674,23 +15674,23 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>Presidente Intercontinental</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>2949246</v>
+        <v>2941640</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>-3385.57</v>
+        <v>136.01</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.03552772471336742</v>
+        <v>0.03624610761344012</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0</v>
+        <v>46.23611318856148</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -15709,32 +15709,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Oyo Rooms</t>
+          <t>Oasis</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2930835</v>
+        <v>2781631</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>404.22</v>
+        <v>0</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.01886458978414001</v>
+        <v>0.01060672677288972</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>137.9197395963949</v>
+        <v>0</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15744,11 +15744,11 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Oasis</t>
+          <t>Las Brisas</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2781631</v>
+        <v>2757193</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>0</v>
@@ -15757,14 +15757,14 @@
         <v>0</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.01060672677288972</v>
+        <v>0.2007099249127645</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -15779,32 +15779,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>Palace</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2757193</v>
+        <v>2646781</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>0</v>
+        <v>4248.74</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.2007099249127645</v>
+        <v>0.065691872504752</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1605.2480352549</v>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15814,32 +15814,32 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Palace</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>2646781</v>
+        <v>2325379</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>4248.74</v>
+        <v>463.18</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.065691872504752</v>
+        <v>0.01119774453970729</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1605.2480352549</v>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+        <v>199.1847350474912</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15849,32 +15849,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>2454033</v>
+        <v>2264171</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>463.18</v>
+        <v>793.92</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.0107855110342852</v>
+        <v>0.006386443426755311</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>188.7423681751631</v>
+        <v>350.6448938706484</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15884,32 +15884,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>Oyo Rooms</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>2331584</v>
+        <v>2206757</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>888.28</v>
+        <v>404.22</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.006260979660179518</v>
+        <v>0.02366051178267476</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>380.9770525102248</v>
+        <v>183.1737703788863</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>2310257</v>
+        <v>1956405</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>4</v>
@@ -15932,19 +15932,19 @@
         <v>1331.05</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.1539945555840757</v>
+        <v>0.109311211124486</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>576.1480216270311</v>
+        <v>680.3550389617692</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15954,32 +15954,32 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Palladium Hotel Group</t>
+          <t>Pueblo Bonito</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>1873865</v>
+        <v>1805513</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>76.16000000000065</v>
+        <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.1021701136421247</v>
+        <v>0.0729443653964275</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>40.64326939240588</v>
+        <v>0</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15989,27 +15989,27 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Oxo Hotel</t>
+          <t>Palladium Hotel Group</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>1812722</v>
+        <v>1753626</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>327.04</v>
+        <v>76.16000000000065</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.009153637457922395</v>
+        <v>0.08252272719496631</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>180.4137644933972</v>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>43.43001301303736</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -16024,32 +16024,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Pueblo Bonito</t>
+          <t>Hoteles Geh Suites</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>1805513</v>
+        <v>1729874</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>0</v>
+        <v>994.65</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.0729443653964275</v>
+        <v>0.006079055468779808</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>574.9840739845791</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16059,32 +16059,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Geh Suites</t>
+          <t>Oxo Hotel</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>1794253</v>
+        <v>1677159</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1103.29</v>
+        <v>327.04</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.0062443813665074</v>
+        <v>0.009647862844250307</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>614.9021347602595</v>
+        <v>194.9964195404252</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16094,32 +16094,32 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>Hoteles Movich</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1612809</v>
+        <v>1571819</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>0</v>
+        <v>5835.68</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.1295633890931908</v>
+        <v>0.03204885549799309</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>3712.692110223888</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16129,27 +16129,27 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Movich</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>1571819</v>
+        <v>1445763</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>5835.68</v>
+        <v>11263.12</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.03204885549799309</v>
+        <v>0.02134167218278514</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>3712.692110223888</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>7790.433148448259</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -16164,32 +16164,32 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Alsol</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1445763</v>
+        <v>1336290</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>11263.12</v>
+        <v>0</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.02134167218278514</v>
+        <v>0.02240681289241108</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>7790.433148448259</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1400931</v>
+        <v>1332737</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>13</v>
@@ -16212,7 +16212,7 @@
         <v>-488.76</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.04107625571851861</v>
+        <v>0.04302049091456154</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>0</v>
@@ -16234,32 +16234,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Alsol</t>
+          <t>BH Hoteles</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1336290</v>
+        <v>1296204</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>0</v>
+        <v>1466.25</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.02240681289241108</v>
+        <v>0.0321808912794591</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1131.187683420202</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1316335</v>
+        <v>1240149</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>9</v>
@@ -16282,14 +16282,14 @@
         <v>3247.33</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.03135751917255106</v>
+        <v>0.0283635272858342</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>2466.948003357808</v>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>2618.499873805486</v>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -16304,32 +16304,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>BH Hoteles</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>1296204</v>
+        <v>1131129</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>1466.25</v>
+        <v>0</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.0321808912794591</v>
+        <v>0.1389434803634245</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>1131.187683420202</v>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1270151</v>
+        <v>1105843</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
@@ -16352,7 +16352,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.02908709279447877</v>
+        <v>0.024620131429145</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>0</v>
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1155820</v>
+        <v>1096832</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>0</v>
@@ -16387,7 +16387,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.04779810005018082</v>
+        <v>0.04691876239934648</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0</v>
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1067555</v>
+        <v>1001637</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>1</v>
@@ -16422,7 +16422,7 @@
         <v>-152.24</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.04928083330601234</v>
+        <v>0.04485956489227135</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>0</v>
@@ -16448,7 +16448,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>1034083</v>
+        <v>692766</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>0</v>
@@ -16457,7 +16457,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.05929698099668982</v>
+        <v>0.05525530987375246</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>0</v>
@@ -16479,11 +16479,11 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>On Vacation</t>
+          <t>Velas Resorts</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>664073</v>
+        <v>662840</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>0</v>
@@ -16492,14 +16492,14 @@
         <v>0</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.0398947103706972</v>
+        <v>0.01770713897773218</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
@@ -16514,32 +16514,32 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Velas Resorts</t>
+          <t>EM Hotels</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>662840</v>
+        <v>586184</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>0</v>
+        <v>1433.46</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.01770713897773218</v>
+        <v>0.02583830333137719</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0</v>
+        <v>2445.409632470351</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16553,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>610189</v>
+        <v>544126</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.005318024415386052</v>
+        <v>0.005125651044059648</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0</v>
@@ -16584,32 +16584,32 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>EM Hotels</t>
+          <t>Regency &amp; Santorini</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>586184</v>
+        <v>530256</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>1433.46</v>
+        <v>0</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.02583830333137719</v>
+        <v>0.02283802540659606</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>2445.409632470351</v>
+        <v>0</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16619,32 +16619,32 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Regency &amp; Santorini</t>
+          <t>Ostar</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>530256</v>
+        <v>437019</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>0</v>
+        <v>206.12</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.02283802540659606</v>
+        <v>0.01202693704392715</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0</v>
+        <v>471.6499740285892</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16654,32 +16654,32 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Ostar</t>
+          <t>Dorado Plaza</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>493644</v>
+        <v>419311</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>206.12</v>
+        <v>277.17</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.02653329119770523</v>
+        <v>0.007185597325135757</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>417.5478685044283</v>
+        <v>661.0129474304276</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16689,32 +16689,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Dorado Plaza</t>
+          <t>Hoteles Cosmos</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>464474</v>
+        <v>382858</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>277.17</v>
+        <v>0</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.006777559131404555</v>
+        <v>0.01842197368214847</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>596.7395376275099</v>
+        <v>0</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16724,32 +16724,32 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Atlantica</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>449997</v>
+        <v>372649</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>0</v>
+        <v>3.780000000000001</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.07337826696622422</v>
+        <v>0.02950766002323903</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>10.1435935692837</v>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16759,32 +16759,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Cosmos</t>
+          <t>DOT Hotels</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>441646</v>
+        <v>357453</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>0</v>
+        <v>156.55</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.01625283598175915</v>
+        <v>0.01422005130744461</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0</v>
+        <v>437.9596758175201</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16794,32 +16794,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>El Dorado San Andrés</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>440121</v>
+        <v>343089</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>3.780000000000001</v>
+        <v>0</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.02537711220323502</v>
+        <v>0.009344514105669376</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>8.588547240417979</v>
+        <v>0</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16829,11 +16829,11 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>El Dorado San Andrés</t>
+          <t>Station Casinos</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>408949</v>
+        <v>298222</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -16842,14 +16842,14 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.008338448070541805</v>
+        <v>0.03540986245146233</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -16864,32 +16864,32 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>DOT Hotels</t>
+          <t>Grupo Welcome</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>357453</v>
+        <v>285193</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>156.55</v>
+        <v>0</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.01422005130744461</v>
+        <v>0.0159506018731175</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>437.9596758175201</v>
+        <v>0</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16899,11 +16899,11 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Prisma Hoteles</t>
+          <t>Costa del Sol</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>355736</v>
+        <v>282981</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>0</v>
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.02387725729192435</v>
+        <v>0.004565677554323437</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>0</v>
@@ -16934,11 +16934,11 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Station Casinos</t>
+          <t>Prisma Hoteles</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>351112</v>
+        <v>278020</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -16947,14 +16947,14 @@
         <v>0</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.03262776549932785</v>
+        <v>0.02481476152794763</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -16969,11 +16969,11 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Blue Doors</t>
+          <t>Atlantica</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>313124</v>
+        <v>276196</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>0</v>
@@ -16982,14 +16982,14 @@
         <v>0</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.01252538930264049</v>
+        <v>0.06195962287650799</v>
       </c>
       <c r="G73" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -17004,11 +17004,11 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Grupo Welcome</t>
+          <t>On Vacation</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>285193</v>
+        <v>267857</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>0</v>
@@ -17017,14 +17017,14 @@
         <v>0</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.0159506018731175</v>
+        <v>0.0443669569957104</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -17039,11 +17039,11 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Costa del Sol</t>
+          <t>Blue Doors</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>282981</v>
+        <v>247963</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>0</v>
@@ -17052,7 +17052,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.004565677554323437</v>
+        <v>0.007408363344531241</v>
       </c>
       <c r="G75" s="13" t="n">
         <v>0</v>
@@ -17074,32 +17074,32 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Hotel Gallery</t>
+          <t>HODELPA</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>248135</v>
+        <v>179609</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>0</v>
+        <v>333.68</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.004856227456827936</v>
+        <v>0.02512680322255566</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0</v>
+        <v>1857.813361245817</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17109,11 +17109,11 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>ePhoneix</t>
+          <t>Fontan</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>239099</v>
+        <v>167918</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>0</v>
@@ -17122,14 +17122,14 @@
         <v>0</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.107378115341344</v>
+        <v>0.01130909134220274</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -17144,32 +17144,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>HODELPA</t>
+          <t>Quinta Real</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>238190</v>
+        <v>167766</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>333.68</v>
+        <v>0</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.03379235064444352</v>
+        <v>0.08070765232526257</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>1400.898442419917</v>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17179,11 +17179,11 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Viaggio</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>231820</v>
+        <v>157775</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>0</v>
@@ -17192,7 +17192,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.007449745492192219</v>
+        <v>0.002218348914593567</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>206210</v>
+        <v>143037</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>0</v>
@@ -17227,7 +17227,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.004054119586828961</v>
+        <v>0.002502848913218258</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>0</v>
@@ -17249,11 +17249,11 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Fontan</t>
+          <t>ePhoneix</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>167918</v>
+        <v>124143</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>0</v>
@@ -17262,14 +17262,14 @@
         <v>0</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.01130909134220274</v>
+        <v>0.1485786552604658</v>
       </c>
       <c r="G81" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -17284,20 +17284,20 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Quinta Real</t>
+          <t>Nacional Inn</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>167766</v>
+        <v>123928</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.08070765232526257</v>
+        <v>0.1937253889355109</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0</v>
@@ -17307,9 +17307,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17319,11 +17319,11 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Viaggio</t>
+          <t>Playa Resorts</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>157775</v>
+        <v>120952</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>0</v>
@@ -17332,14 +17332,14 @@
         <v>0</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.002218348914593567</v>
+        <v>0.1084314438785634</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -17354,11 +17354,11 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Zona Estrategica</t>
+          <t>BlueBay</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>130946</v>
+        <v>117507</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>0</v>
@@ -17367,14 +17367,14 @@
         <v>0</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.01212713637682709</v>
+        <v>0.1889844860306195</v>
       </c>
       <c r="G84" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -17389,11 +17389,11 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Aristos</t>
+          <t>Hotel Gallery</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>127111</v>
+        <v>115197</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>0</v>
@@ -17402,14 +17402,14 @@
         <v>0</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.04453587809080253</v>
+        <v>0.008081807685964044</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -17424,310 +17424,30 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Nacional Inn</t>
+          <t>Zar</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>123928</v>
+        <v>106844</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.1937253889355109</v>
+        <v>0.001263524390700461</v>
       </c>
       <c r="G86" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Playa Resorts</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="n">
-        <v>120952</v>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="14" t="n">
-        <v>0.1084314438785634</v>
-      </c>
-      <c r="G87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>BlueBay</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="n">
-        <v>117507</v>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="14" t="n">
-        <v>0.1889844860306195</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Sonesta</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="n">
-        <v>108213</v>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="14" t="n">
-        <v>0.08695812887545858</v>
-      </c>
-      <c r="G89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Zar</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="n">
-        <v>106844</v>
-      </c>
-      <c r="D90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="14" t="n">
-        <v>0.001263524390700461</v>
-      </c>
-      <c r="G90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>Ayenda Hoteles</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="n">
-        <v>101227</v>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="14" t="n">
-        <v>0.002430181670898081</v>
-      </c>
-      <c r="G91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>Red Roof</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>72039</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="14" t="n">
-        <v>0.02266827690556504</v>
-      </c>
-      <c r="G92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>MasHoteles</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>68099</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="14" t="n">
-        <v>0.033377876327112</v>
-      </c>
-      <c r="G93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>The Q Project</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>66547</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="14" t="n">
-        <v>0.05026522608081507</v>
-      </c>
-      <c r="G94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -17752,7 +17472,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -17775,7 +17495,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17836,19 +17556,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>58509409</v>
+        <v>56517000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>19611.28</v>
+        <v>19704</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.04082915963140218</v>
+        <v>0.0402734221561654</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>335.1816457417986</v>
+        <v>348.6384627634163</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -17871,16 +17591,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>56633748</v>
+        <v>55431331</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>-3260.47</v>
+        <v>-3666.32</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.03885437707566167</v>
+        <v>0.03913119098655596</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>0</v>
@@ -17906,7 +17626,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>51206443</v>
+        <v>50344123</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>278</v>
@@ -17915,10 +17635,10 @@
         <v>28694.97</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.03961081616233332</v>
+        <v>0.03884360047348526</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>560.3781149180778</v>
+        <v>569.9765591308443</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
@@ -17941,7 +17661,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>37997376</v>
+        <v>35540876</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>52</v>
@@ -17950,10 +17670,10 @@
         <v>16730.35</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.0400463442528242</v>
+        <v>0.03933845074612117</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>440.3027724861843</v>
+        <v>470.7354427617373</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -17976,7 +17696,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>35188603</v>
+        <v>34433925</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>60</v>
@@ -17985,10 +17705,10 @@
         <v>7964.27</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.03470208805959134</v>
+        <v>0.03380671822918822</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>226.3309515299599</v>
+        <v>231.2913790687527</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -18007,32 +17727,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>33414685</v>
+        <v>32159621</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>35125.63</v>
+        <v>2316.7</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.03736168693495091</v>
+        <v>0.03022498306183397</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1051.203385577329</v>
+        <v>72.03754049215941</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18042,32 +17762,32 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>33269951</v>
+        <v>30545585</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>2316.7</v>
+        <v>34793.68</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.03014867680448342</v>
+        <v>0.03721634403138784</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>69.63340583218773</v>
+        <v>1139.073944728837</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18081,7 +17801,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>29933474</v>
+        <v>28689653</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>5</v>
@@ -18090,10 +17810,10 @@
         <v>5684.65</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.02725991644003633</v>
+        <v>0.02766614151798908</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>189.9094638998467</v>
+        <v>198.1428635612986</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -18116,19 +17836,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>24065961</v>
+        <v>23559250</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>378.160000000001</v>
+        <v>-857.5199999999991</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.08032311695344307</v>
+        <v>0.07809153517196006</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>15.71348013071246</v>
+        <v>0</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -18151,19 +17871,19 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>22795611</v>
+        <v>22091372</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>5232.81</v>
+        <v>8434.450000000001</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.02347802829237611</v>
+        <v>0.02283149276559193</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>229.5533995557303</v>
+        <v>381.7983781179367</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -18186,7 +17906,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>18824416</v>
+        <v>17398386</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
@@ -18195,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.1080036161546791</v>
+        <v>0.108292343899026</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0</v>
@@ -18217,32 +17937,32 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Bogotá Area</t>
+          <t>Los Cabos Area</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>17037011</v>
+        <v>15930225</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>7341.63</v>
+        <v>2593.1</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.0163668967520183</v>
+        <v>0.03011608436164586</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>430.9224194314367</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>162.7786173767163</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18256,19 +17976,19 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>17030994</v>
+        <v>15860464</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>11178.35</v>
+        <v>10862.95</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.01798685385010411</v>
+        <v>0.01763044258982587</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>656.3533520122196</v>
+        <v>684.9074528967122</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -18287,27 +18007,27 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Los Cabos Area</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>16752933</v>
+        <v>14710428</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>2593.1</v>
+        <v>1450.34</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.03085614918892113</v>
+        <v>0.01735646304784606</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>154.7848367805207</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>98.59264461917762</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -18322,32 +18042,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Bogotá Area</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>16456477</v>
+        <v>14709415</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>1450.34</v>
+        <v>6708.11</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.01855299891951357</v>
+        <v>0.01440308809017898</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>88.13186443246632</v>
+        <v>456.0419296076696</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18357,32 +18077,32 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>15306108</v>
+        <v>13164582</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>1489.69</v>
+        <v>0</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.01158269626739861</v>
+        <v>0.04938614837903703</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>97.32650520955426</v>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18392,32 +18112,32 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>14314614</v>
+        <v>13135637</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>0</v>
+        <v>917.38</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.05254434384329189</v>
+        <v>0.01283820495344078</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>69.83901884621201</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18427,23 +18147,23 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>13782879</v>
+        <v>13129556</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>917.38</v>
+        <v>1013.9</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.01517578439163545</v>
+        <v>0.01164837561909938</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>66.55938864441892</v>
+        <v>77.22271796548185</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
@@ -18462,27 +18182,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Atlanta Area</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>13292322</v>
+        <v>11752274</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>2129.08</v>
+        <v>387.46</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.01950065609304379</v>
+        <v>0.0862097837405765</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>160.1736701834337</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>32.96893860711553</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -18497,27 +18217,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>Atlanta Area</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>13079553</v>
+        <v>11706545</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>-2852.55</v>
+        <v>1691.54</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.08146646907581627</v>
+        <v>0.02050852749466217</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>144.4952374932143</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -18536,7 +18256,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>11920254</v>
+        <v>11235748</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
@@ -18545,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.01323017110205873</v>
+        <v>0.01339634886791694</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0</v>
@@ -18571,19 +18291,19 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>11482496</v>
+        <v>10233775</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>12739.44</v>
+        <v>11963.16</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.02171374586152697</v>
+        <v>0.01889273508553784</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1109.466095176519</v>
+        <v>1168.987983417654</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
@@ -18602,32 +18322,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>11092649</v>
+        <v>9738022</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>6201.65</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.02628488470157129</v>
+        <v>0.02167945400000123</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>559.0774575126284</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18637,32 +18357,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Medellin Area</t>
+          <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>11066309</v>
+        <v>9715484</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>1204.36</v>
+        <v>2985.84</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.01820851017263299</v>
+        <v>0.01617387255230928</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>108.8312281899954</v>
+        <v>307.3279725436221</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18672,27 +18392,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Houston (and vicinity), TX, US</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>10861009</v>
+        <v>9374264</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>1784.5</v>
+        <v>1326.440000000001</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.008468458133125569</v>
+        <v>0.05397746425746064</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>164.3033349848067</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>141.4980418729407</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -18707,32 +18427,32 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nashville (and vicinity), TN, US</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>10360819</v>
+        <v>9366939</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>2985.84</v>
+        <v>5319.3</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.01564615693025812</v>
+        <v>0.02349913883286739</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>288.1857119596434</v>
+        <v>567.8802861852736</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18742,32 +18462,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale (and vicinity), FL, US</t>
+          <t>Acapulco</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>9968322</v>
+        <v>9361785</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>0</v>
+        <v>12184.91</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.02143931546352535</v>
+        <v>0.03634381691098439</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1301.558410068165</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18777,27 +18497,27 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>9933761</v>
+        <v>9274218</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>1326.440000000001</v>
+        <v>687.01</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.05169190198958884</v>
+        <v>0.007636438996797358</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>133.5284792939956</v>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>74.07740469331215</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -18812,32 +18532,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Acapulco</t>
+          <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>9708589</v>
+        <v>8865602</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>12184.91</v>
+        <v>277.66</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.03973502225709627</v>
+        <v>0.02636087205358418</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1255.064973911245</v>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>31.31879820456637</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18847,32 +18567,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Denver (and vicinity), CO, US</t>
+          <t>Seattle Area</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>9608233</v>
+        <v>8749626</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>277.66</v>
+        <v>0</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.02501188303822357</v>
+        <v>0.0253021100559041</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>28.89813350696221</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18882,32 +18602,32 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Medellin Area</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>9341677</v>
+        <v>8745217</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>2585.95</v>
+        <v>1110</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.00903317466446335</v>
+        <v>0.01904503913396317</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>276.8186054816496</v>
+        <v>126.9265245219187</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18917,32 +18637,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Seattle Area</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>9198616</v>
+        <v>8628582</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>0</v>
+        <v>-277.7400000000002</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.02447183358887902</v>
+        <v>0.03456802056235891</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18952,32 +18672,32 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Merida</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>9056798</v>
+        <v>8609051</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>2078.35</v>
+        <v>4711.73</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.01354242415476198</v>
+        <v>0.03389119195600072</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>229.479557786317</v>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>547.2995804067137</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18987,32 +18707,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Mazatlán</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>8931374</v>
+        <v>8606144</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>4711.73</v>
+        <v>2585.95</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.03356952692833152</v>
+        <v>0.009237935130994787</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>527.5481689603414</v>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>300.4771939674725</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19022,23 +18742,23 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Phoenix (and vicinity), AZ, US</t>
+          <t>Greenville Area</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>8863156</v>
+        <v>8244376</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>579.2</v>
+        <v>1311.68</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.01535683226155559</v>
+        <v>0.01679993731484348</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>65.34918261621482</v>
+        <v>159.0999731210706</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -19057,23 +18777,23 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Riviera Nayarit</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>8842457</v>
+        <v>8107259</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>-277.7400000000002</v>
+        <v>1208.22</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.03406948996189633</v>
+        <v>0.04558149677961441</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0</v>
+        <v>149.0294068562507</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -19092,23 +18812,23 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Greenville Area</t>
+          <t>Phoenix (and vicinity), AZ, US</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>8707289</v>
+        <v>7759961</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>1311.68</v>
+        <v>579.2</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.01668946557303886</v>
+        <v>0.01690163133551831</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>150.6416061302203</v>
+        <v>74.6395503791836</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
@@ -19127,32 +18847,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Merida</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>8466072</v>
+        <v>7149395</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>1208.22</v>
+        <v>2078.35</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.04508312709837573</v>
+        <v>0.01533430451108101</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>142.7131732401992</v>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>290.702919617674</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19166,7 +18886,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>7637527</v>
+        <v>7013670</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>1</v>
@@ -19175,7 +18895,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.01490050378872638</v>
+        <v>0.0140392975432263</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>0</v>
@@ -19197,32 +18917,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Washington, DC Area</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>6950763</v>
+        <v>6338383</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1649.7</v>
+        <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.01726731295542662</v>
+        <v>0.02341827560751693</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>237.3408502059414</v>
+        <v>0</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19232,32 +18952,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Washington, DC Area</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>6928973</v>
+        <v>6152432</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>400.63</v>
+        <v>1450.52</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.02224456640255345</v>
+        <v>0.01711241993410086</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>57.81953544919283</v>
+        <v>235.7636784933178</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19271,7 +18991,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>6494710</v>
+        <v>5974500</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>2</v>
@@ -19280,19 +19000,19 @@
         <v>1274.57</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.08511157542061154</v>
+        <v>0.08321248640053561</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>196.2474075054929</v>
+        <v>213.335007113566</v>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19306,19 +19026,19 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>6451769</v>
+        <v>5928182</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>729.8200000000002</v>
+        <v>223.34</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.01532990409297047</v>
+        <v>0.01449550637952748</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>113.1193630770104</v>
+        <v>37.67428192994075</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -19337,32 +19057,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Ixtapa / Zihuatanejo</t>
+          <t>Honolulu Area</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>5826208</v>
+        <v>5659600</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>10210.77</v>
+        <v>1888.44</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.02574212935755126</v>
+        <v>0.0148287864866775</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1752.558439382871</v>
+        <v>333.670224044102</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19372,32 +19092,32 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Honolulu Area</t>
+          <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>5733726</v>
+        <v>5571650</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>1888.44</v>
+        <v>10210.77</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.01493269821404092</v>
+        <v>0.02470955641506556</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>329.3565126760504</v>
+        <v>1832.629472418404</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19407,32 +19127,32 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Múnich Area</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>5731428</v>
+        <v>5418441</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>2478.46</v>
+        <v>0</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.04796186918862105</v>
+        <v>0.00499497918312666</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>432.433243512786</v>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19442,32 +19162,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Múnich Area</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>5590460</v>
+        <v>5218966</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>0</v>
+        <v>2478.46</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.005067203772140396</v>
+        <v>0.048193837629906</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>474.8948354904018</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19481,28 +19201,28 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>5556041</v>
+        <v>4560225</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>1777.6</v>
+        <v>-156.8200000000001</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.01416908190562309</v>
+        <v>0.01549375304946576</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>319.9400436389868</v>
+        <v>0</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19512,32 +19232,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Berlin Area</t>
+          <t>Tampa Area</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>5466392</v>
+        <v>4537424</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>2350.62</v>
+        <v>2645.24</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.07961101216305014</v>
+        <v>0.006586997380011213</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>430.0130689493179</v>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>582.9827673146702</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19547,32 +19267,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Tampa Area</t>
+          <t>Berlin Area</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>5348153</v>
+        <v>4534864</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>2645.24</v>
+        <v>2350.62</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.006632009218883603</v>
+        <v>0.07780542040511028</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>494.6081385480184</v>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
+        <v>518.3441002861387</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19582,32 +19302,32 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Santa Marta Area</t>
+          <t>Pittsburgh Area</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>5111963</v>
+        <v>4416339</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>2689.71</v>
+        <v>989.38</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.01116205262049041</v>
+        <v>0.009642828596264913</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>526.1599115643052</v>
+        <v>224.0271863188039</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19617,32 +19337,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Cozumel</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>4924697</v>
+        <v>4405816</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>2417.94</v>
+        <v>-623.25</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.04375984959074639</v>
+        <v>0.0330497233656603</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>490.982490902486</v>
+        <v>0</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19652,32 +19372,32 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Huatulco Area</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>4885333</v>
+        <v>4364128</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>5970.57</v>
+        <v>2417.94</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.05006291280451097</v>
+        <v>0.04148549263449651</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1222.141868322999</v>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>554.0488271654727</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19687,32 +19407,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Panama City Area</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>4780143</v>
+        <v>4274711</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>752.27</v>
+        <v>1072.34</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.02765858678286403</v>
+        <v>0.02966633299888577</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>157.3739530386434</v>
+        <v>250.8567245832525</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19722,32 +19442,32 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Huatulco Area</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>4622337</v>
+        <v>4236031</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>0</v>
+        <v>5692.05</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.1693911543013848</v>
+        <v>0.05566484286824152</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0</v>
+        <v>1343.722460954606</v>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19757,32 +19477,32 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Cozumel</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>4587785</v>
+        <v>4067110</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>-623.25</v>
+        <v>0</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.03241106547059202</v>
+        <v>0.1752989223305984</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19792,32 +19512,32 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Pittsburgh Area</t>
+          <t>Santa Marta Area</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>4530821</v>
+        <v>3877714</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>989.38</v>
+        <v>2613.74</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.009562726048987589</v>
+        <v>0.008495985005598658</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>218.3666050810659</v>
+        <v>674.0414584469098</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19827,32 +19547,32 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Minneapolis - St. Paul Area</t>
+          <t>Panama City Area</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>4443385</v>
+        <v>3728396</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>950.24</v>
+        <v>0</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.004973235495011124</v>
+        <v>0.02949606211357377</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>213.8549776803046</v>
+        <v>0</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19862,32 +19582,32 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Minneapolis - St. Paul Area</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>4339939</v>
+        <v>3671279</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>1072.34</v>
+        <v>0</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.03096909887443118</v>
+        <v>0.004310214505625969</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>247.0864221824316</v>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19897,32 +19617,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Columbus (and vicinity), OH, US</t>
+          <t>Salt Lake City Area</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>3991096</v>
+        <v>3534747</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>0</v>
+        <v>567.28</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.01029717150376739</v>
+        <v>0.01093090962380052</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0</v>
+        <v>160.4867335625435</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19932,32 +19652,32 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>London Area</t>
+          <t>Hawái</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>3934495</v>
+        <v>3510164</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>535.24</v>
+        <v>1874.83</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.03459859524538728</v>
+        <v>0.02113775880557148</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>136.0377888394826</v>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
+        <v>534.1146453556015</v>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19967,32 +19687,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>London Area</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3870505</v>
+        <v>3360139</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>1070.02</v>
+        <v>535.24</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.02761112567998233</v>
+        <v>0.0351220589386332</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>276.4548812105914</v>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>159.2910293294414</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20002,32 +19722,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Salt Lake City Area</t>
+          <t>Ottawa Area</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>3769126</v>
+        <v>3307145</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>567.28</v>
+        <v>6446.25</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.01059396793845576</v>
+        <v>0.0203634857256032</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>150.507040624272</v>
+        <v>1949.188801821511</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20041,28 +19761,28 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>3643534</v>
+        <v>3300927</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>728.5799999999999</v>
+        <v>340.09</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.006670995796937808</v>
+        <v>0.007087403023453715</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>199.965198623095</v>
+        <v>103.0286340776394</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20072,32 +19792,32 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Hawái</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>3624895</v>
+        <v>3206133</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>1874.83</v>
+        <v>-1241.41</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.02060804519855058</v>
+        <v>0.04163302021469478</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>517.2094639982674</v>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20107,32 +19827,32 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Ottawa Area</t>
+          <t>Istanbul Area</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>3560028</v>
+        <v>3171029</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>6446.25</v>
+        <v>0</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.01980124875422328</v>
+        <v>0.1158062572117757</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>1810.730140324739</v>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20142,11 +19862,11 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Istanbul Area</t>
+          <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>3502658</v>
+        <v>3126372</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -20155,14 +19875,14 @@
         <v>0</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.1113719923555197</v>
+        <v>0.007427139188810544</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -20177,32 +19897,32 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>3435767</v>
+        <v>3074776</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>6176.809999999999</v>
+        <v>0</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.03653652881583647</v>
+        <v>0.007815528675910051</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>1797.796532768374</v>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20212,32 +19932,32 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Veracruz Area</t>
+          <t>Barranquilla Area</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>3419807</v>
+        <v>3059835</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>2047.77</v>
+        <v>2509.42</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.04668567553666039</v>
+        <v>0.01165520363026111</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>598.796949652422</v>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>820.1161173723419</v>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20247,32 +19967,32 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Barranquilla Area</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>3401051</v>
+        <v>3028604</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>2886.27</v>
+        <v>1070.02</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.0107049262125149</v>
+        <v>0.03172781915364307</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>848.6406113874799</v>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>353.3046908740793</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20282,32 +20002,32 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Calgary Area</t>
+          <t>Veracruz Area</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>3330582</v>
+        <v>2916491</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>378.7</v>
+        <v>2047.77</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.01607196580057179</v>
+        <v>0.04673184316358254</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>113.7038511587464</v>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>702.13486000814</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20317,20 +20037,20 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Portland (and vicinity), OR, US</t>
+          <t>Key West Area</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>3326773</v>
+        <v>2862570</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>0</v>
+        <v>-19333.83</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.007494349629505829</v>
+        <v>0.01174888299674768</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0</v>
@@ -20340,9 +20060,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20352,32 +20072,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Bayahibe</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>3326509</v>
+        <v>2839184</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>-1241.41</v>
+        <v>2653.91</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.04268649205518458</v>
+        <v>0.1294326116236214</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>934.7439264239302</v>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20387,20 +20107,20 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Detroit Area</t>
+          <t>Long Island Area</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>3164847</v>
+        <v>2719003</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>-414.9</v>
+        <v>0</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.0122599923471814</v>
+        <v>0.006325112550445881</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
@@ -20410,9 +20130,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20422,32 +20142,32 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Indianápolis Area</t>
+          <t>Calgary Area</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>3037705</v>
+        <v>2713755</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>472.74</v>
+        <v>0</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.01657205028138019</v>
+        <v>0.01022789455938358</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>155.6240648779259</v>
+        <v>0</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20457,32 +20177,32 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Long Island Area</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>3017731</v>
+        <v>2697499</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>0</v>
+        <v>5732.03</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.007667018697160217</v>
+        <v>0.01974050778146721</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0</v>
+        <v>2124.942400349361</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20492,20 +20212,20 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>San Jose Area</t>
+          <t>Detroit Area</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>2972373</v>
+        <v>2644621</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>0</v>
+        <v>-414.9</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.02163860323048285</v>
+        <v>0.01329944820070626</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0</v>
@@ -20515,9 +20235,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20527,32 +20247,32 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Eje cafetero</t>
+          <t>Cleveland Area</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>2927573</v>
+        <v>2590593</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>1846.42</v>
+        <v>0</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.01635279461861412</v>
+        <v>0.009184383652700369</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>630.6999005661003</v>
+        <v>0</v>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20562,32 +20282,32 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Indianápolis Area</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2920375</v>
+        <v>2543439</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>694.8499999999999</v>
+        <v>0</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.04116491888884133</v>
+        <v>0.01616865983418513</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>237.9317724607285</v>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20597,32 +20317,32 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Bayahibe</t>
+          <t>Raleigh Area</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>2896702</v>
+        <v>2540949</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>2653.91</v>
+        <v>0</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.1286318026500482</v>
+        <v>0.004453454201560126</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>916.1833008711286</v>
-      </c>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20632,32 +20352,32 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Raleigh Area</t>
+          <t>Niagara Falls, Canada</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>2893185</v>
+        <v>2540569</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>0</v>
+        <v>467.1</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.004785037942613418</v>
+        <v>0.1248767500508744</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>183.8564510548621</v>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20667,11 +20387,11 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Rome Area</t>
+          <t>Vienna Area</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>2890300</v>
+        <v>2533670</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>0</v>
@@ -20680,7 +20400,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.1770885375220565</v>
+        <v>0.06234395165905584</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>0</v>
@@ -20702,11 +20422,11 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Area</t>
+          <t>San Luis, Misuri Area</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>2885428</v>
+        <v>2499614</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>0</v>
@@ -20715,7 +20435,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.008730420582319157</v>
+        <v>0.005092786326208768</v>
       </c>
       <c r="G88" s="13" t="n">
         <v>0</v>
@@ -20737,32 +20457,32 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Key West Area</t>
+          <t>Eje cafetero</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>2862570</v>
+        <v>2413742</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>-19333.83</v>
+        <v>1846.42</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.01174888299674768</v>
+        <v>0.01638658978465801</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0</v>
+        <v>764.9616239018089</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20772,32 +20492,32 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Niagara Falls, Canada</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2793456</v>
+        <v>2410329</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>467.1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>0.1141485672228236</v>
+        <v>0.179007927963361</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>167.2122274344038</v>
+        <v>0</v>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20807,32 +20527,32 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Santiago de Cali Area</t>
+          <t>San Jose Area</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>2695967</v>
+        <v>2393057</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.01531287289495754</v>
+        <v>0.02444112279816152</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>222.5546529315826</v>
+        <v>0</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20842,32 +20562,32 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Vienna Area</t>
+          <t>West Palm Beach Area</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>2694764</v>
+        <v>2345911</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>0</v>
+        <v>382.16</v>
       </c>
       <c r="F92" s="14" t="n">
-        <v>0.06573896638072944</v>
+        <v>0.005655372262630594</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>162.9047308273844</v>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20877,32 +20597,32 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>West Palm Beach Area</t>
+          <t>Hamburg Area</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>2678151</v>
+        <v>2343106</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>382.16</v>
+        <v>0</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.005258852096091669</v>
+        <v>0.08357411060361759</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>142.6954641467191</v>
-      </c>
-      <c r="H93" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0</v>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20912,32 +20632,32 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Hamburg Area</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>2645047</v>
+        <v>2313600</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>0</v>
+        <v>616.96</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.08040877912566392</v>
+        <v>0.03933480290456431</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="8" t="inlineStr">
+        <v>266.6666666666667</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20947,11 +20667,11 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>San Luis, Misuri Area</t>
+          <t>Rome Area</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>2594903</v>
+        <v>2309530</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>0</v>
@@ -20960,14 +20680,14 @@
         <v>0</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>0.005217150698889323</v>
+        <v>0.1907180248795209</v>
       </c>
       <c r="G95" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
@@ -20982,23 +20702,23 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Manzanillo</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>2530348</v>
+        <v>2306866</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>-1067.71</v>
+        <v>139.1600000000001</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>0.09036504069795934</v>
+        <v>0.08526026219121527</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0</v>
+        <v>60.32426677579021</v>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
@@ -21017,32 +20737,32 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Sacramento Area</t>
+          <t>Puerto Escondido Area</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>2495261</v>
+        <v>2231508</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>0</v>
+        <v>11654.01</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.007943056858581127</v>
+        <v>0.02855512953572203</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0</v>
+        <v>5222.481837394264</v>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21052,32 +20772,32 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>Curacao Area</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>2481761</v>
+        <v>2204595</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>0</v>
+        <v>861.5200000000002</v>
       </c>
       <c r="F98" s="14" t="n">
-        <v>0.1748524535601938</v>
+        <v>0.01477459578743488</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="8" t="inlineStr">
+        <v>390.783794755953</v>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21091,7 +20811,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>2410225</v>
+        <v>2159868</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>0</v>
@@ -21100,7 +20820,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.2005995290896078</v>
+        <v>0.2040027446121708</v>
       </c>
       <c r="G99" s="13" t="n">
         <v>0</v>
@@ -21122,32 +20842,32 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Puerto Escondido Area</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>2380978</v>
+        <v>2156983</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>12374.82</v>
+        <v>1083.54</v>
       </c>
       <c r="F100" s="14" t="n">
-        <v>0.02733414588459028</v>
+        <v>0.008624082804546906</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>5197.368476315195</v>
+        <v>502.3405376862034</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21157,32 +20877,32 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>2378738</v>
+        <v>2068464</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>1083.54</v>
+        <v>-1067.71</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.00834770369834761</v>
+        <v>0.09745975757857038</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>455.5104429323448</v>
-      </c>
-      <c r="H101" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I101" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21192,32 +20912,32 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Manzanillo</t>
+          <t>Puerto Plata</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>2353476</v>
+        <v>2004593</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>139.1600000000001</v>
+        <v>889.48</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>0.08358615086790773</v>
+        <v>0.0625598313473109</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>59.12955985104588</v>
+        <v>443.7209947355897</v>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -21227,11 +20947,11 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Portland (and vicinity), ME, US</t>
+          <t>Sacramento Area</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>2298332</v>
+        <v>1907000</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>0</v>
@@ -21240,7 +20960,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>0.005919510323138695</v>
+        <v>0.006513371788148925</v>
       </c>
       <c r="G103" s="13" t="n">
         <v>0</v>
@@ -21262,32 +20982,32 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Curacao Area</t>
+          <t>Reno Area</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>2272636</v>
+        <v>1902543</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>861.5200000000002</v>
+        <v>217.08</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.01462750744069882</v>
+        <v>0.1223656968594139</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>379.0840240144045</v>
-      </c>
-      <c r="H104" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I104" s="8" t="inlineStr">
+        <v>114.0999178467977</v>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21297,32 +21017,32 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Oaxaca</t>
+          <t>Portland (and vicinity), ME, US</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>2184498</v>
+        <v>1888497</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>824.39</v>
+        <v>0</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>0.01756971166831007</v>
+        <v>0.00566482234284725</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>377.381897351245</v>
+        <v>0</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21368,7 +21088,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21429,19 +21149,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>651411954</v>
+        <v>583972351</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>71645.31999999999</v>
+        <v>61807.97</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.02062558403710227</v>
+        <v>0.02156991162069589</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>109.9846564989503</v>
+        <v>105.8405760035718</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -21464,28 +21184,28 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>291908002</v>
+        <v>264927309</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1102</v>
+        <v>1064</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>175959.57</v>
+        <v>174294.13</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.03283921966620155</v>
+        <v>0.03259224967253187</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>602.7911835044522</v>
+        <v>657.8941622058298</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21499,19 +21219,19 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>71015098</v>
+        <v>59957914</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>30153.35</v>
+        <v>26046.44</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.01632927409323578</v>
+        <v>0.01568738698948065</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>424.6047791133091</v>
+        <v>434.4120444216921</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -21534,19 +21254,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>48643177</v>
+        <v>42899036</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>11030.53</v>
+        <v>13087.25</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.05734859793388906</v>
+        <v>0.06034960785599005</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>226.7641770191121</v>
+        <v>305.0709577716385</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
@@ -21569,28 +21289,28 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>34881467</v>
+        <v>33533846</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>10497.6</v>
+        <v>5344.480000000001</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.077004846155123</v>
+        <v>0.07587835287369066</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>300.950645223723</v>
+        <v>159.3756946340125</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21600,23 +21320,23 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>27999264</v>
+        <v>22482236</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>4980.35</v>
+        <v>792.0300000000001</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.06235285327500037</v>
+        <v>0.1023835440567388</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>177.8743184106554</v>
+        <v>35.22914713643252</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -21635,27 +21355,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Gran Bretaña (UK)</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>26919051</v>
+        <v>21151130</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>792.0300000000001</v>
+        <v>706.87</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.1011836561400326</v>
+        <v>0.04421314605886305</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>29.42265683883135</v>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>33.41996385063115</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -21670,32 +21390,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Gran Bretaña (UK)</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>26671114</v>
+        <v>20756037</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1134.93</v>
+        <v>4905.809999999999</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.04360061600726539</v>
+        <v>0.06066991497461678</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>42.55277826040562</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>236.3558130099691</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -21709,19 +21429,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>9766707</v>
+        <v>8297114</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>1780.37</v>
+        <v>-68.66999999999996</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.1806861821492136</v>
+        <v>0.185008666868986</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>182.2896908855769</v>
+        <v>0</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -21740,11 +21460,11 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>6109606</v>
+        <v>5418441</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -21753,14 +21473,14 @@
         <v>0</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.1461153141462805</v>
+        <v>0.00499497918312666</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -21775,32 +21495,32 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>5590460</v>
+        <v>4274711</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0</v>
+        <v>1072.34</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.005067203772140396</v>
+        <v>0.02966633299888577</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0</v>
+        <v>250.8567245832525</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -21810,20 +21530,20 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>5132300</v>
+        <v>4050373</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.1223373536231319</v>
+        <v>0.1672359557996264</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0</v>
@@ -21833,9 +21553,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21849,23 +21569,23 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>4579220</v>
+        <v>3894480</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>289.66</v>
+        <v>-462.61</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.04759522364070737</v>
+        <v>0.05007626178591237</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>63.25531422381978</v>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -21880,32 +21600,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>4339939</v>
+        <v>3425781</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1072.34</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.03096909887443118</v>
+        <v>0.1254814595562296</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>247.0864221824316</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21919,7 +21639,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>4019880</v>
+        <v>3424732</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
@@ -21928,7 +21648,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.1201147795456581</v>
+        <v>0.1128047391737514</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0</v>
@@ -21950,32 +21670,32 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>3663361</v>
+        <v>3206133</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>7682.029999999999</v>
+        <v>-1241.41</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.1232963390722345</v>
+        <v>0.04163302021469478</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>2096.989622371369</v>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21985,32 +21705,32 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>3361554</v>
+        <v>2750892</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>-1067.71</v>
+        <v>7682.029999999999</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.08270133396637389</v>
+        <v>0.122471183892352</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0</v>
+        <v>2792.559649742701</v>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22020,32 +21740,32 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>3326509</v>
+        <v>2614265</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>-1241.41</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.04268649205518458</v>
+        <v>0.06103895358733716</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22059,7 +21779,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>3118504</v>
+        <v>2506456</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>1</v>
@@ -22068,10 +21788,10 @@
         <v>221.81</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.06675187846480235</v>
+        <v>0.06622298576156932</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>71.12705322808628</v>
+        <v>88.49546930007948</v>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
@@ -22094,7 +21814,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>3117635</v>
+        <v>2483133</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -22103,7 +21823,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.04298354361559323</v>
+        <v>0.04319905538688423</v>
       </c>
       <c r="G25" s="13" t="n">
         <v>0</v>
@@ -22129,19 +21849,19 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>3058639</v>
+        <v>2464666</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>-760.9400000000001</v>
+        <v>100.16</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.03018499404473689</v>
+        <v>0.03256871316438009</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0</v>
+        <v>40.63836641557111</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
@@ -22160,32 +21880,32 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>3025638</v>
+        <v>2234507</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1146.22</v>
+        <v>-1067.71</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.0483769043091077</v>
+        <v>0.09087463140639077</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>378.8358025646161</v>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22195,32 +21915,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2878412</v>
+        <v>2225910</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>0</v>
+        <v>818.9499999999998</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.06969120473372123</v>
+        <v>0.01190793877560189</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+        <v>367.9169418350247</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22230,23 +21950,23 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>2649148</v>
+        <v>2204595</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>892.0599999999998</v>
+        <v>861.5200000000002</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.01131382618109671</v>
+        <v>0.01477459578743488</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>336.73467847021</v>
+        <v>390.783794755953</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
@@ -22265,32 +21985,32 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Emiratos Árabes Unidos</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>2521523</v>
+        <v>1997347</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>0</v>
+        <v>1146.22</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.07051809561126351</v>
+        <v>0.04809379642095239</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>573.8712402001254</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22300,32 +22020,32 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>2272636</v>
+        <v>1813987</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>861.5200000000002</v>
+        <v>0</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.01462750744069882</v>
+        <v>0.2404361221993322</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>379.0840240144045</v>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22335,32 +22055,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Hungría</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>2015688</v>
+        <v>1205870</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>339.12</v>
+        <v>3235.19</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.06391217291564964</v>
+        <v>0.1061971854345825</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>168.2403229071166</v>
+        <v>2682.867970842628</v>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22370,32 +22090,32 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Grecia</t>
+          <t>Emiratos Árabes Unidos</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1890278</v>
+        <v>1017766</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.2343702883914429</v>
+        <v>0.04321720316850828</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22405,32 +22125,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Hungría</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1674183</v>
+        <v>1008480</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>3235.19</v>
+        <v>0</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.1017606796867487</v>
+        <v>0.3671039584324924</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1932.399265791135</v>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22440,32 +22160,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>1393902</v>
+        <v>1007542</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>702.55</v>
+        <v>0</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.02328427679994719</v>
+        <v>0.05496247302841966</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>504.0167816675777</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22479,19 +22199,19 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>1309936</v>
+        <v>938714</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>3852.22</v>
+        <v>3700.65</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.1151834898804216</v>
+        <v>0.1345010301327135</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>2940.769625386279</v>
+        <v>3942.255042536918</v>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
@@ -22510,32 +22230,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>1288636</v>
+        <v>916973</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>0</v>
+        <v>702.55</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.03956586654415987</v>
+        <v>0.02051532596924882</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>766.1621443597576</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22545,11 +22265,11 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>1069731</v>
+        <v>841988</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>0</v>
@@ -22558,14 +22278,14 @@
         <v>0</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.3466432215201766</v>
+        <v>0.006716247737497447</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -22580,11 +22300,11 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>1007542</v>
+        <v>580742</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>0</v>
@@ -22593,14 +22313,14 @@
         <v>0</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.05496247302841966</v>
+        <v>0.03594711593099862</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -22615,11 +22335,11 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>1006998</v>
+        <v>511342</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>0</v>
@@ -22628,14 +22348,14 @@
         <v>0</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.009844110911838951</v>
+        <v>0.05899574061978089</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -22650,11 +22370,11 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>898060</v>
+        <v>498307</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>0</v>
@@ -22663,7 +22383,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.05485825000556756</v>
+        <v>0.08362314797905709</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>0</v>
@@ -22685,32 +22405,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>799618</v>
+        <v>495526</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>0</v>
+        <v>497.7</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.06852021840428804</v>
+        <v>0.01303867001933299</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1004.387257177222</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22720,20 +22440,20 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>679253</v>
+        <v>453647</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.02224208063858386</v>
+        <v>0.01373975800567401</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>0</v>
@@ -22743,9 +22463,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22755,23 +22475,23 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>643407</v>
+        <v>445815</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>497.7</v>
+        <v>344.75</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.012012614099629</v>
+        <v>0.00779022688783464</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>773.5383668502208</v>
+        <v>773.3028274059868</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -22790,32 +22510,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>517030</v>
+        <v>438649</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.0127884262035085</v>
+        <v>0.3165674605436237</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22825,11 +22545,11 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>502327</v>
+        <v>405705</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>0</v>
@@ -22838,14 +22558,14 @@
         <v>0</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.2881111307972695</v>
+        <v>0.004320873541119779</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I46" s="11" t="inlineStr">
@@ -22860,32 +22580,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Islas Caimán</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>445815</v>
+        <v>234688</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>344.75</v>
+        <v>0</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.00779022688783464</v>
+        <v>0.002386146713935097</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>773.3028274059868</v>
+        <v>0</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22895,11 +22615,11 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Mónaco</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>405705</v>
+        <v>228233</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>0</v>
@@ -22908,14 +22628,14 @@
         <v>0</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.004320873541119779</v>
+        <v>0.1322245249372352</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -22930,11 +22650,11 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Islas Caimán</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>362965</v>
+        <v>203240</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>0</v>
@@ -22943,7 +22663,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.002077335280261182</v>
+        <v>0.02286951387522141</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>0</v>
@@ -22965,11 +22685,11 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kirguistán</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>320182</v>
+        <v>187934</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>0</v>
@@ -22978,7 +22698,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.09902180634763977</v>
+        <v>0.1369150872114679</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>0</v>
@@ -23000,11 +22720,11 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>318827</v>
+        <v>174979</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>0</v>
@@ -23013,14 +22733,14 @@
         <v>0</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.0109401023125394</v>
+        <v>0.1357991530412221</v>
       </c>
       <c r="G51" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
@@ -23035,11 +22755,11 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>275619</v>
+        <v>143235</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>0</v>
@@ -23048,14 +22768,14 @@
         <v>0</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.1395077988092258</v>
+        <v>0.01882919677453137</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
@@ -23070,11 +22790,11 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>265688</v>
+        <v>138369</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>0</v>
@@ -23083,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.001080214386799554</v>
+        <v>0.001091284897628804</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0</v>
@@ -23105,11 +22825,11 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Åland</t>
+          <t>Santa Lucía</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>253700</v>
+        <v>130760</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>0</v>
@@ -23118,7 +22838,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.01493102089081592</v>
+        <v>0.003548485775466504</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>0</v>
@@ -23144,7 +22864,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>252877</v>
+        <v>130727</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
@@ -23153,14 +22873,14 @@
         <v>0</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.02481838996824543</v>
+        <v>0.03955571534572047</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
@@ -23175,11 +22895,11 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>251825</v>
+        <v>116784</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>0</v>
@@ -23188,14 +22908,14 @@
         <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.003049736920480493</v>
+        <v>0.1777298260035621</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -23210,11 +22930,11 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>250657</v>
+        <v>115834</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>0</v>
@@ -23223,7 +22943,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.03975552248690441</v>
+        <v>0.03890912858055493</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>0</v>
@@ -23245,11 +22965,11 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Mónaco</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>228233</v>
+        <v>89943</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>0</v>
@@ -23258,14 +22978,14 @@
         <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.1322245249372352</v>
+        <v>0.03815749974984157</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
@@ -23280,11 +23000,11 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>217480</v>
+        <v>88437</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>0</v>
@@ -23293,7 +23013,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.009623873459628469</v>
+        <v>0.0174361409817158</v>
       </c>
       <c r="G59" s="13" t="n">
         <v>0</v>
@@ -23315,11 +23035,11 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Kirguistán</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>187934</v>
+        <v>87144</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>0</v>
@@ -23328,14 +23048,14 @@
         <v>0</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.1369150872114679</v>
+        <v>0.009168732213348022</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -23350,11 +23070,11 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>175174</v>
+        <v>86640</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>0</v>
@@ -23363,7 +23083,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.01419160377681619</v>
+        <v>0.007906278855032318</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0</v>
@@ -23385,11 +23105,11 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Kenia</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>163929</v>
+        <v>85626</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>0</v>
@@ -23398,7 +23118,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.01381085713937132</v>
+        <v>0.002545955667671035</v>
       </c>
       <c r="G62" s="13" t="n">
         <v>0</v>
@@ -23420,11 +23140,11 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Santa Lucía</t>
+          <t>Sint Maarten</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>130760</v>
+        <v>81663</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>0</v>
@@ -23433,7 +23153,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.003548485775466504</v>
+        <v>0.01817224446811898</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>0</v>
@@ -23455,11 +23175,11 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Croacia (Hrvatska)</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>130514</v>
+        <v>78596</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>0</v>
@@ -23468,717 +23188,17 @@
         <v>0</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.03418790321344837</v>
+        <v>0.0009669703292788439</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Maldivas</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="n">
-        <v>124713</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>0.004851138213337823</v>
-      </c>
-      <c r="G65" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Eslovenia</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="n">
-        <v>115834</v>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>0.03890912858055493</v>
-      </c>
-      <c r="G66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Eslovaquia</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>113786</v>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>0.01979153850210044</v>
-      </c>
-      <c r="G67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Mauricio</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="n">
-        <v>113494</v>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>0.09018978976862214</v>
-      </c>
-      <c r="G68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>San Cristóbal y Nieves</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="n">
-        <v>107064</v>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="14" t="n">
-        <v>0.01981058058731226</v>
-      </c>
-      <c r="G69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Laos</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>88437</v>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="14" t="n">
-        <v>0.0174361409817158</v>
-      </c>
-      <c r="G70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="n">
-        <v>86640</v>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="14" t="n">
-        <v>0.007906278855032318</v>
-      </c>
-      <c r="G71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="n">
-        <v>85626</v>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="14" t="n">
-        <v>0.002545955667671035</v>
-      </c>
-      <c r="G72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Sint Maarten</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="n">
-        <v>81663</v>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>0.01817224446811898</v>
-      </c>
-      <c r="G73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Montenegro</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>75120</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="14" t="n">
-        <v>0.1661741214057508</v>
-      </c>
-      <c r="G74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Albania</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="n">
-        <v>72472</v>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="14" t="n">
-        <v>0.3281681201015564</v>
-      </c>
-      <c r="G75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Belice</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="n">
-        <v>68133</v>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="14" t="n">
-        <v>0.002436411137040788</v>
-      </c>
-      <c r="G76" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Guam</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="n">
-        <v>58538</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="14" t="n">
-        <v>0.02902388192285353</v>
-      </c>
-      <c r="G77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Anguila</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="n">
-        <v>58377</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="14" t="n">
-        <v>0.00380286756770646</v>
-      </c>
-      <c r="G78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Estonia</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="n">
-        <v>55499</v>
-      </c>
-      <c r="D79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="14" t="n">
-        <v>0.004396475612173193</v>
-      </c>
-      <c r="G79" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="n">
-        <v>51302</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="14" t="n">
-        <v>0.02251374215430198</v>
-      </c>
-      <c r="G80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="n">
-        <v>49531</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>0.003815792130181099</v>
-      </c>
-      <c r="G81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Rumania</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>48988</v>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="14" t="n">
-        <v>0.0293337143790316</v>
-      </c>
-      <c r="G82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="n">
-        <v>45796</v>
-      </c>
-      <c r="D83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="14" t="n">
-        <v>0.002423792470958162</v>
-      </c>
-      <c r="G83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>Nueva Zelanda (Aotearoa)</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>45640</v>
-      </c>
-      <c r="D84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="14" t="n">
-        <v>0.01794478527607362</v>
-      </c>
-      <c r="G84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17495,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_B2C_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17495,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21088,7 +21088,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
